--- a/docs/demo-scenarios.xlsx
+++ b/docs/demo-scenarios.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Scenarios'!$A$1:$L$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Scenarios'!$A$1:$L$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/pos-uplink-watch.txt — 14 samples, window 2026-09-11 14:32:58.460877+00 to 2026-09-11 14:39:30.022613+00</t>
+          <t>docs/demo-screens/scenarios/pos-uplink-watch-instance-80612-healthy.txt — 14 samples, window 2026-09-11 14:32:58.460877+00 to 2026-09-11 14:39:30.022613+00</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>DIRECT CONSEQUENCE, observed this run: the WAITER device enrolled at 14:14:23 UTC still could not pair at 14:22, because GET /api/session answers 401 'device credential not cached locally' until a config pull delivers it. S-CUI-03 is that 401 on screen, and it is what blocks demo step 1a end to end. ONE ALTERNATIVE IS NOT EXCLUDED: the contact at 14:20:13 UTC fell close to the POS process disappearing, so it cannot be told apart from the SHUTDOWN drain — which would mean zero periodic ticks rather than a slow one. Either reading leaves the measured gap as it stands; separating them needs a run where the process is watched staying up across several ticks, which this environment did not provide.</t>
+          <t>MEASURED ON A PROCESS WATCHED STAYING UP THROUGHOUT, which is what makes the number mean anything: across a process start and a process stop, the startup drain and the shutdown drain are indistinguishable from periodic ticks, and a first attempt at this measurement spanned exactly that and had to be thrown away. See S-SYNC-12 for what that first attempt DID find, which is a different defect and a real one.</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -4419,129 +4419,187 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>S-CHAIN-01</t>
+          <t>S-SYNC-12</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1a / 3</t>
+          <t>1a / 6</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>The KDS LAN socket accepts an authenticated client and delivers a ticket snapshot</t>
+          <t>A live POS keeps pumping for as long as it keeps serving</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>POS process, ws 9310</t>
+          <t>POS process -&gt; backend 8080 -&gt; postgres 5432</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>POS process hosting the LAN hub; enrolled KDS device token from apps/kds/.env.dev</t>
+          <t>Two POS instances were observed this run. pid 74104 (started 14:04:44 UTC) and, after the operator restarted it, pid 80612 (started 14:31:36 UTC). The pump interval is 60s and S-SYNC-09 confirms pid 80612 hits it: contacts at 14:36:38, 14:37:39, 14:38:39.</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Connect to /kds?outlet_id=..&amp;device_id=.., send the {type:auth} first frame, wait 2s</t>
+          <t>Sample device_credential.last_used_at for the POS device across both instances and compare the contact pattern while each process was demonstrably still serving LAN requests</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Socket opens, auth accepted, a snapshot frame arrives</t>
+          <t>Contact every ~60s for as long as the process is alive</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Socket open; auth accepted (not closed); frames=2; snapshot carried 0 ticket(s)</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>pid 80612: contacts 60-61s apart, exactly as documented. pid 74104: LAST contact at 14:07:47, about three minutes after start, then NOTHING for the remaining ~12 minutes of its life — while it was still serving 9320 (S-CUI-01 recorded HTTP 200 and a real captain 401 body from it at 14:22) and still hosting 9310. It then exited without the operator touching it.</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>live ws 9310 session held open by this stage</t>
+          <t>docs/demo-screens/scenarios/pos-uplink-watch-instance-74104-stalled.txt (12 samples, one contact change in 19 minutes) against pos-uplink-watch-instance-80612-healthy.txt (14 samples, 60s cadence)</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>A plain ws://host:9310 connect with no path and no auth frame is REJECTED at the handshake, which from outside is indistinguishable from the socket being down. The path and the first-frame auth are both required (apps/kds/src/lib/lanClient.ts:56-61).</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>NEW ROW this re-run. The earlier pass never held a socket open across a send, so it could not separate 'the order was created' from 'the kitchen received it'.</t>
-        </is>
-      </c>
+          <t>THE PUMP IS NOT SLOW — IT STOPPED, AND THE PROCESS DID NOT. This is worse than a long interval, because every outward sign of health stayed green: the till served the LAN, the captain listener answered, the KDS socket accepted clients. Nothing surfaced that the outlet had gone silent toward the cloud. MEASURED CONSEQUENCE: the WAITER device enrolled at 14:14:23 could not pair until 14:31:37 — seventeen minutes — because the config pull that delivers a credential to device_credential_cache rides this same loop, and what finally delivered it was the STARTUP pull of the replacement process, not a tick. NOT DIAGNOSED HERE: whether the pump thread died, wedged on the database lock, or the process was already failing. This run observed the symptom on one instance and could not reproduce it on the second, so it is reported as an observation with its artefacts, not as a root cause. The first measurement's own conclusion ('the pump interval is 12m27s') was WRONG and is superseded by this row: it spanned a process boundary, where a startup drain and a shutdown drain cannot be told apart from periodic ticks.</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>S-CHAIN-01</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1a / 3</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>The KDS LAN socket accepts an authenticated client and delivers a ticket snapshot</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>POS process, ws 9310</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>POS process hosting the LAN hub; enrolled KDS device token from apps/kds/.env.dev</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Connect to /kds?outlet_id=..&amp;device_id=.., send the {type:auth} first frame, wait 2s</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Socket opens, auth accepted, a snapshot frame arrives</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Socket open; auth accepted (not closed); frames=2; snapshot carried 0 ticket(s)</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>live ws 9310 session held open by this stage</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>A plain ws://host:9310 connect with no path and no auth frame is REJECTED at the handshake, which from outside is indistinguishable from the socket being down. The path and the first-frame auth are both required (apps/kds/src/lib/lanClient.ts:56-61).</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>NEW ROW this re-run. The earlier pass never held a socket open across a send, so it could not separate 'the order was created' from 'the kitchen received it'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
           <t>S-CHAIN-02</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>THE CENTRAL CLAIM — pair, pick a table, add an item with a free modifier, send, and the KOT arrives on the KDS socket</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>captain 9320 -&gt; edge db -&gt; ws 9310</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Paired WAITER device; table T1; item "Butter Chicken" with free modifier "Spice/Hot"; socket held open from S-CHAIN-01 BEFORE the send</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>POST /api/orders (1 line, default variant, one 0-paise modifier) -&gt; POST /api/orders/{id}/send -&gt; count frames that arrived on the socket opened beforehand</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>201 created, 200 sent, at least one KOT frame on the socket</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>CHAIN STOPS AT CREATE. POST /api/orders -&gt; HTTP 400 {"code":"STORAGE_ERROR","message":"sqlite error: FOREIGN KEY constraint failed"}. Nothing was sent, so no KOT frame could arrive and the socket stayed silent.</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>live captain listener + live ws 9310, same process</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>The free modifier is deliberate: a 0-paise modifier still has to reach the stored line, and a price-changing one would hide a dropped modifier behind a changed total.</t>
         </is>
       </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>RE-RUN with the POS back up. The chain now gets further than before — pairing, tables and menu all succeed — but it stops at order create, which the earlier run could not reach at all.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L69"/>
+  <autoFilter ref="A1:L70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4552,7 +4610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4613,7 +4671,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -4643,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
@@ -4832,95 +4890,95 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>S-SYNC-04</t>
+          <t>S-SYNC-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4 / 5 / 6</t>
+          <t>1a / 6</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>KNOWN GAP A7 — aggregates other than `order` never reach the cloud</t>
+          <t>A live POS keeps pumping for as long as it keeps serving</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>kot=0, invoice=0, payment=0, stock_count=0, stock_ledger_entry=39, cash_shift=0, table_session=0</t>
+          <t>pid 80612: contacts 60-61s apart, exactly as documented. pid 74104: LAST contact at 14:07:47, about three minutes after start, then NOTHING for the remaining ~12 minutes of its life — while it was still serving 9320 (S-CUI-01 recorded HTTP 200 and a real captain 401 body from it at 14:22) and still hosting 9310. It then exited without the operator touching it.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>S-ADM-08</t>
+          <t>S-SYNC-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 / 5 / 6</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Orders screen</t>
+          <t>KNOWN GAP A7 — aggregates other than `order` never reach the cloud</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>NOT BUILT. The admin console has three tabs — Menu and pricing, Suppliers, Goods receipts. There is no orders screen, no order route in apps/admin/src/lib/api.ts, and no component for one. Demo step 4 has no surface.</t>
+          <t>kot=0, invoice=0, payment=0, stock_count=0, stock_ledger_entry=39, cash_shift=0, table_session=0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>S-ADM-09</t>
+          <t>S-ADM-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Stock variance screen</t>
+          <t>Orders screen</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>NOT BUILT. No stock, variance or count screen exists in the admin console and no inventory endpoint is wired into apps/admin/src/lib/api.ts. Demo step 5 has no surface — and gap A7 means the underlying stock_count rows never reach the cloud either (S-SYNC-04), so the data is absent as well as the screen.</t>
+          <t>NOT BUILT. The admin console has three tabs — Menu and pricing, Suppliers, Goods receipts. There is no orders screen, no order route in apps/admin/src/lib/api.ts, and no component for one. Demo step 4 has no surface.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>S-SYNC-03</t>
+          <t>S-ADM-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>A replayed order's device_id resolves to a real device row in the cloud</t>
+          <t>Stock variance screen</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Across all orders: &lt;no device row&gt; x4</t>
+          <t>NOT BUILT. No stock, variance or count screen exists in the admin console and no inventory endpoint is wired into apps/admin/src/lib/api.ts. Demo step 5 has no surface — and gap A7 means the underlying stock_count rows never reach the cloud either (S-SYNC-04), so the data is absent as well as the screen.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>S-SYNC-08</t>
+          <t>S-SYNC-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4930,76 +4988,98 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Cloud variant coverage matches the edge, so a replayed order item does not violate its FK</t>
+          <t>A replayed order's device_id resolves to a real device row in the cloud</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>variants-per-item histogram (variants|items): 0|12, 1|9, 2|22</t>
+          <t>Across all orders: &lt;no device row&gt; x4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>S-BE-09</t>
+          <t>S-SYNC-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pre</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>A rate-limited login is indistinguishable from a wrong password</t>
+          <t>Cloud variant coverage matches the edge, so a replayed order item does not violate its FK</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>HTTP 401 {"code":"unauthorized","message":"authentication required"} for a correct password, identical to the wrong-password body; no Retry-After; recovery only by waiting out the window</t>
+          <t>variants-per-item histogram (variants|items): 0|12, 1|9, 2|22</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>S-CAP-06</t>
+          <t>S-BE-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>pre</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Every menu item carries at least one variant, so no line needs a null variant_id</t>
+          <t>A rate-limited login is indistinguishable from a wrong password</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>12 of 43 items have no variant: Aloo Tikki Chaat, Egg Bhurji, Filter Coffee, Gajar Halwa, Gulab Jamun (2 pc), …</t>
+          <t>HTTP 401 {"code":"unauthorized","message":"authentication required"} for a correct password, identical to the wrong-password body; no Retry-After; recovery only by waiting out the window</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
+          <t>S-CAP-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Every menu item carries at least one variant, so no line needs a null variant_id</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>12 of 43 items have no variant: Aloo Tikki Chaat, Egg Bhurji, Filter Coffee, Gajar Halwa, Gulab Jamun (2 pc), …</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
           <t>S-API-02</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>PATCH /menu/items/{itemId} refuses an identity field rather than ignoring it</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>HTTP 400 invalid_input</t>
         </is>

--- a/docs/demo-scenarios.xlsx
+++ b/docs/demo-scenarios.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Scenarios'!$A$1:$L$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Scenarios'!$A$1:$L$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,10 +40,6 @@
     <font>
       <b val="1"/>
       <color rgb="00991B1B"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0092400E"/>
     </font>
     <font>
       <b val="1"/>
@@ -85,12 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -126,16 +122,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -503,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -620,7 +613,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>backend=UP, captain=UP, kdsUi=UP, adminUi=UP, posVite=UP, kdsSocket=UP. holler-pos process: 80612@2026-09-11T20:01:36.4807624+05:30</t>
+          <t>backend=UP, captain=UP, kdsUi=UP, adminUi=UP, posVite=UP, kdsSocket=UP. holler-pos process: 55508@2026-09-11T20:50:29.4480541+05:30</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -682,7 +675,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>holler-pos running: 80612@2026-09-11T20:01:36.4807624+05:30</t>
+          <t>holler-pos running: 55508@2026-09-11T20:50:29.4480541+05:30</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -1353,7 +1346,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>WAITER enrolled in S-BE-06 (token 01a090d1…/len=80); credential cached at the edge</t>
+          <t>WAITER enrolled in S-BE-06 (token 01a09111…/len=80); credential cached at the edge</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1368,7 +1361,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200; device_kind=WAITER; outlet_name=Tandoori Junction — Camp, Pune; device_id=01a090d1-cbb5-7084-975c-b90686207a07</t>
+          <t>HTTP 200; device_kind=WAITER; outlet_name=Tandoori Junction — Camp, Pune; device_id=01a09111-126f-7e32-9f4d-6f35b064cb14</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1762,27 +1755,23 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400; order_id=n/a; status=n/a; lines=0</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>HTTP 201; order_id=01a09114-08bd-7a73-9af1-ddd39e018190; status=DRAFT; lines=1</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400 STORAGE_ERROR sqlite error: FOREIGN KEY constraint failed; order n/a, 0 line(s)</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>DIAGNOSIS. The edge answers STORAGE_ERROR 'sqlite error: FOREIGN KEY constraint failed'. The order insert touches four referents and three of them were just read back from this same API — table_id from GET /api/tables, menu_item_id and variant_id from GET /api/menu — while outlet_id is the configured one the till uses every day. That leaves device_id, which is the ONE value the captain path supplies differently: `"order".device_id TEXT NOT NULL REFERENCES device(id)` (packages/contracts/sqlite/0001_init.sql:69, rebuilt at 0035:53), and the attribution override writes the WAITER's device id resolved from the credential. The config bundle carries device_credentialS into device_credential_cache; it does not carry the `device` ROW itself, so the edge can AUTHENTICATE the waiter and cannot REFERENCE it. CONFIRMING COMPARISON: the till creates orders on this same database fine (4 in the cloud), and the only value that differs between the two paths is device_id.</t>
-        </is>
-      </c>
+          <t>HTTP 201  ; order 01a09114-08bd-7a73-9af1-ddd39e018190, 1 line(s)</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>STILL FAIL, but no longer for an unknown reason. The 400 is a sqlite FOREIGN KEY violation and the column is isolated in S-CAP-19.</t>
+          <t>T30: WAS FAIL (400 STORAGE_ERROR, sqlite FOREIGN KEY constraint failed). NOW PASS — 201 with a DRAFT order carrying its line. 758a70b mints the `device` row that "order".device_id references.</t>
         </is>
       </c>
     </row>
@@ -1799,48 +1788,52 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>order.device_id is the WAITER's device, not the till's</t>
+          <t>order.device_id is the WAITER's device, not the till's, and it resolves to a real device row</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>captain 9320</t>
+          <t>captain 9320 -&gt; postgres 5432</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>An order created from the captain API</t>
+          <t>Waiter device 01a09111-126f-7e32-9f4d-6f35b064cb14; the till is a different row in the device table</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Create the order from the captain API, wait for it to replay, then read "order".device_id in Postgres and LEFT JOIN device on it.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>device_id == 01a09111-126f-7e32-9f4d-6f35b064cb14, joining to a device row of kind WAITER</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED by S-CAP-10: POST /api/orders returns 400 STORAGE_ERROR and no order is created</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>cloud "order".device_id=01a09111-126f-7e32-9f4d-6f35b064cb14 -&gt; device kind=WAITER, name="T30 Backfill Probe". Waiter device is 01a09111-126f-7e32-9f4d-6f35b064cb14; match=true.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400 sqlite error: FOREIGN KEY constraint failed</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
+          <t>postgres: select o.device_id, d.kind from "order" o left join device d on d.id=o.device_id where o.id='01a09114-08bd-7a73-9af1-ddd39e018190'</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>WHICH SIDE WAS CHECKED: the CLOUD. The edge SQLite file is encrypted at rest and exposes no read surface, so the edge's own row is not directly observable here — but the cloud copy is a replay of it, so a WAITER device_id in Postgres could only have been written by the edge. THE KNOWN TRAP this guards: create_order_impl takes device_id from state.device_id, which is the TILL; the captain path overrides it with the resolved credential's device. If that override regressed, every captain order would read as till-authored and would look entirely correct in review.</t>
+        </is>
+      </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>STILL BLOCKED, new reason. It was blocked by pairing (the phone could not authenticate at all); the phone now authenticates, lists tables and lists the menu, and this is blocked one step further on by the order-create foreign key in S-CAP-19.</t>
+          <t>WAS FAIL, on a check that could not have passed: it read device_id off the CanonicalOrder, which does not carry the field, so the row reported '&lt;absent from CanonicalOrder&gt;' regardless of attribution. Now asserted against Postgres, with the join that proves the id resolves.</t>
         </is>
       </c>
     </row>
@@ -1867,38 +1860,38 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>An order created from the captain API</t>
+          <t>Order 01a09114-08bd-7a73-9af1-ddd39e018190 in DRAFT with one line</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>POST /api/orders/{orderId}/items with one more line</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>201 CanonicalOrder now carrying two lines</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED by S-CAP-10: POST /api/orders returns 400 STORAGE_ERROR and no order is created</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>HTTP 201; lines=2</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400 sqlite error: FOREIGN KEY constraint failed</t>
+          <t>HTTP 201, 2 lines</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>STILL BLOCKED, new reason. It was blocked by pairing (the phone could not authenticate at all); the phone now authenticates, lists tables and lists the menu, and this is blocked one step further on by the order-create foreign key in S-CAP-19.</t>
+          <t>T30: WAS BLOCKED by the order-create foreign key of S-CAP-19 — the phone authenticated, listed tables and listed the menu, and could not create an order. NOW PASS: 758a70b mints the `device` row the credential points at, so the create succeeds and every step after it could be exercised for the first time.</t>
         </is>
       </c>
     </row>
@@ -1925,38 +1918,42 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>An order created from the captain API</t>
+          <t>An item carrying at least one modifier with price_delta_paise == 0</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>POST /api/orders/{orderId}/items with modifiers:[{price_delta_paise:0}] and read the echoed line</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>201 and the modifier present on the returned CanonicalOrder line</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED by S-CAP-10: POST /api/orders returns 400 STORAGE_ERROR and no order is created</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>HTTP 201; free modifier "Spice/Hot" (0 paise) sent; present on the returned line = true</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400 sqlite error: FOREIGN KEY constraint failed</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+          <t>HTTP 201, order 01a09114-08bd-7a73-9af1-ddd39e018190, modifier Hot</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Only free modifiers are selectable in the reduced scope (docs/captain-api.md).</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>STILL BLOCKED, new reason. It was blocked by pairing (the phone could not authenticate at all); the phone now authenticates, lists tables and lists the menu, and this is blocked one step further on by the order-create foreign key in S-CAP-19.</t>
+          <t>T30: WAS BLOCKED by the order-create foreign key of S-CAP-19 — the phone authenticated, listed tables and listed the menu, and could not create an order. NOW PASS: 758a70b mints the `device` row the credential points at, so the create succeeds and every step after it could be exercised for the first time.</t>
         </is>
       </c>
     </row>
@@ -1983,38 +1980,38 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>An order created from the captain API</t>
+          <t>Order 01a09114-08bd-7a73-9af1-ddd39e018190 with lines</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>POST /api/orders/{orderId}/send</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>200 {order, kots:[{id,station,sequence,status:'NEW'}]} with at least one KOT</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED by S-CAP-10: POST /api/orders returns 400 STORAGE_ERROR and no order is created</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>HTTP 200; order.status=SENT_TO_KITCHEN; kots=2 (BAR#1/NEW, MAIN#1/NEW)</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400 sqlite error: FOREIGN KEY constraint failed</t>
+          <t>HTTP 200, 2 KOT(s), order status SENT_TO_KITCHEN</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr"/>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>STILL BLOCKED, new reason. It was blocked by pairing (the phone could not authenticate at all); the phone now authenticates, lists tables and lists the menu, and this is blocked one step further on by the order-create foreign key in S-CAP-19.</t>
+          <t>T30: WAS BLOCKED by the order-create foreign key of S-CAP-19 — the phone authenticated, listed tables and listed the menu, and could not create an order. NOW PASS: 758a70b mints the `device` row the credential points at, so the create succeeds and every step after it could be exercised for the first time.</t>
         </is>
       </c>
     </row>
@@ -2041,45 +2038,49 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>An order created from the captain API</t>
+          <t>Order 01a09114-08bd-7a73-9af1-ddd39e018190 already sent (status SENT_TO_KITCHEN)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>POST /api/orders/{orderId}/items after the send</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>201 — append-after-send is legal through DRAFT/CONFIRMED/SENT_TO_KITCHEN/PREPARING</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED by S-CAP-10: POST /api/orders returns 400 STORAGE_ERROR and no order is created</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>HTTP 201; lines now 4; code=</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400 sqlite error: FOREIGN KEY constraint failed</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
+          <t>HTTP 201, 4 lines</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>This is the whole point of append-only: the waiter walks back and adds two more.</t>
+        </is>
+      </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>STILL BLOCKED, new reason. It was blocked by pairing (the phone could not authenticate at all); the phone now authenticates, lists tables and lists the menu, and this is blocked one step further on by the order-create foreign key in S-CAP-19.</t>
+          <t>T30: WAS BLOCKED by the order-create foreign key of S-CAP-19 — the phone authenticated, listed tables and listed the menu, and could not create an order. NOW PASS: 758a70b mints the `device` row the credential points at, so the create succeeds and every step after it could be exercised for the first time.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>S-CAP-18</t>
+          <t>S-CAP-16</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2089,55 +2090,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Isolate WHICH foreign key the captain order create violates</t>
+          <t>Sending an order that does not exist is a 404, not a 500</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>captain 9320 -&gt; edge SQLite</t>
+          <t>captain 9320</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>POST /api/orders fails with STORAGE_ERROR / FOREIGN KEY constraint failed (S-CAP-10)</t>
+          <t>Paired WAITER session</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Vary every referent the API accepts — table, menu item, variant — and then remove the table entirely by ordering TAKEAWAY with table_id null. Watch whether the failure survives each removal.</t>
+          <t>POST /api/orders/{unknown uuid}/send</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>One variation succeeds, or one changes the error, naming the culprit</t>
+          <t>404 ORDER_NOT_FOUND</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>real table + real item + real variant: HTTP 400 STORAGE_ERROR | bogus table_id: HTTP 400 STORAGE_ERROR | bogus menu_item_id: HTTP 400 STORAGE_ERROR | bogus variant_id: HTTP 400 STORAGE_ERROR | TAKEAWAY, table_id null: HTTP 400 STORAGE_ERROR. All five identical = true</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>HTTP 404 code=ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>real table + real item + real variant: HTTP 400 STORAGE_ERROR ; bogus table_id: HTTP 400 STORAGE_ERROR ; bogus menu_item_id: HTTP 400 STORAGE_ERROR ; bogus variant_id: HTTP 400 STORAGE_ERROR ; TAKEAWAY, table_id null: HTTP 400 STORAGE_ERROR</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>THE TAKEAWAY PROBE IS THE DECISIVE ONE. With table_id NULL the table foreign key cannot be the cause, and the item and variant were both read back from GET /api/menu moments earlier. What remains on the `order` row is outlet_id and device_id, and outlet_id is the configured value the till writes successfully every day — four till-authored orders are in the cloud. So the violated key is `"order".device_id REFERENCES device(id)`. The captain resolves the WAITER device from its credential and writes it, correctly and per docs/captain-api.md; the edge has a `device_credential_cache` row for that device (which is why GET /api/session returns 200) but NO `device` row, because the config bundle carries credentials and not the device records they point at. THE PHONE CAN AUTHENTICATE AND CANNOT BE REFERENCED.</t>
-        </is>
-      </c>
+          <t>HTTP 404 ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>S-CAP-19</t>
+          <t>S-CAP-17</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2147,59 +2144,55 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Isolate the column whose foreign key stops every captain order create</t>
+          <t>An out-of-scope captain route is refused rather than half-implemented</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>captain 9320 -&gt; edge sqlite</t>
+          <t>captain 9320</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Paired WAITER device whose credential IS cached (S-CUI-03 passes, so this is not an auth fault)</t>
+          <t>Paired WAITER session</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Create with a real table + real item + real default variant + no modifier; then TAKEAWAY with table_id null. Every referenced row is one the API itself served.</t>
+          <t>POST /api/orders/{orderId}/cancel — explicitly out of scope in docs/captain-api.md</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>A create that references only rows the API served should succeed</t>
+          <t>404, with no order state change</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Both probes -&gt; 400 STORAGE_ERROR "sqlite error: FOREIGN KEY constraint failed". Removing the table, the modifier and the variant delta changes nothing, so the failing key is NOT table_id, menu_item_id, variant_id or modifier_id — all of those were varied or removed. The only foreign key left on the insert is order.device_id, which is "TEXT NOT NULL REFERENCES device(id)" (packages/contracts/sqlite/0035_order_source_widened.sql:53).</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>HTTP 404 code=NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>two live creates against the shipping listener; packages/contracts/sqlite/0035_order_source_widened.sql:53</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>ROOT CAUSE. The captain route attributes the order to the WAITER credential's own device_id (captain.rs handle_create_order). That device is enrolled IN THE CLOUD and its CREDENTIAL reaches the edge — edge/sync/src/config.rs:770 calls replace_device_credential_cache — but the config apply has NO upsert_device call at all, so the `device` ROW never lands at the edge. The phone can therefore authenticate and browse, and can never be the device_id on an order. Credential cached, device row absent: the two halves of the same enrolment travel separately and only one of them travels.</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>NEW ROW this re-run. The earlier sheet attributed the blocked chain to pairing (S-CUI-03). Pairing is now fixed and the chain still stops, one step further on, for an unrelated reason — so the earlier cause was real but was not the only one.</t>
-        </is>
-      </c>
+          <t>No cancel, no line removal, no quantity edit, no payment — out of scope, explicitly.</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>S-CUI-01</t>
+          <t>S-CAP-18</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2209,32 +2202,32 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>The captain page is served by the POS process and renders the pair screen at phone width</t>
+          <t>The order-create foreign keys accept real referents and still reject bogus ones</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>captain 9320 (Chromium 390×844)</t>
+          <t>captain 9320 -&gt; edge SQLite</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>POS process hosts the captain listener and serves apps/captain/dist</t>
+          <t>A WAITER device whose `device` row exists at the edge (S-CAP-19)</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Navigate to http://localhost:9320/ in a 390px mobile context</t>
+          <t>Vary every referent the API accepts — table, menu item, variant — and then remove the table entirely by ordering TAKEAWAY with table_id null. Watch which variations are accepted and which are refused.</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>200, 'Pair this phone' visible, no console errors</t>
+          <t>Real referents -&gt; 201; a bogus menu_item_id or variant_id -&gt; 400; a bogus table_id -&gt; 201, because table_id has no FK</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200; pair heading visible=true; console errors=0</t>
+          <t>real table + real item + real variant: HTTP 201  | bogus table_id: HTTP 201  | bogus menu_item_id: HTTP 400 STORAGE_ERROR | bogus variant_id: HTTP 400 STORAGE_ERROR | TAKEAWAY, table_id null: HTTP 201 . All five identical = false</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2244,20 +2237,24 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/captain-01-pair.png</t>
+          <t xml:space="preserve">real table + real item + real variant: HTTP 201  ; bogus table_id: HTTP 201  ; bogus menu_item_id: HTTP 400 STORAGE_ERROR ; bogus variant_id: HTTP 400 STORAGE_ERROR ; TAKEAWAY, table_id null: HTTP 201 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Real listener, real bundle — nothing intercepted.</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr"/>
+          <t>HISTORY. This row existed to isolate a failure by elimination, because SQLite's 'FOREIGN KEY constraint failed' names no column. The answer it reached was `"order".device_id REFERENCES device(id)`: the config bundle carried device_credentialS but not the `device` ROWS they point at, so a paired phone could AUTHENTICATE and could never be REFERENCED. 758a70b mints that row during config apply and the same five probes now separate cleanly. NOTE THE BOGUS-TABLE PROBE: it returns 201, and that is correct rather than a hole — `order.table_id` is nullable with no REFERENCES clause, deliberately, so a table that has not synced never blocks an order. Read a 201 there as the schema behaving as written.</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>WAS FAIL (all five probes identical: 400 STORAGE_ERROR). NOW PASS — real referents create, a bogus menu_item_id or variant_id is still refused, so the fix opened the path without weakening the keys.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>S-CUI-02</t>
+          <t>S-CAP-19</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2267,32 +2264,32 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Pairing the page with a garbage token is refused and the bad token is not persisted</t>
+          <t>The foreign key that stopped every captain order create is satisfied</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>captain 9320 (Chromium 390×844)</t>
+          <t>captain 9320 -&gt; edge sqlite</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Pair screen showing, localStorage empty</t>
+          <t>Paired WAITER device whose credential IS cached AND whose `device` row exists at the edge</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Paste a fabricated credential_id.secret, tap Pair, then read localStorage</t>
+          <t>Create with a real table + real item + real default variant + no modifier; then TAKEAWAY with table_id null. Every referenced row is one the API itself served.</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>A rejection message, and NOTHING stored — a mistyped token is never persisted as though it worked</t>
+          <t>A create that references only rows the API served should succeed</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>message="That device token was rejected. Check it and paste it again."; localStorage token stored=false</t>
+          <t>Both probes -&gt; 201. The order.device_id -&gt; device(id) foreign key is now satisfied for a device whose credential arrived in a post-fix config bundle. Created 01a09112-4bb3-7941-be34-762ea1baf2bb, 01a09112-4f72-72f2-af23-b081bfddac13.</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2302,20 +2299,24 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/captain-02-garbage-token.png</t>
+          <t>two live creates against the shipping listener (holler-pos pid 55508, built 20:50:27 IST)</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Falsifier for S-CUI-03: a page that stores whatever is typed would show a 'paired' state either way.</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
+          <t>ROOT CAUSE, now fixed (758a70b). The captain route attributes the order to the WAITER credential's own device_id (captain.rs handle_create_order). The credential reached the edge but the `device` ROW it points at did not, because `device` has no Postgres mirror and no AggregateType — it is not a config family on /sync/config at all. config::apply_bundle now mints the row from the credential before caching it. SCOPE LIMIT: see S-CAP-20 — the fix only fires for credentials that ARRIVE in a bundle.</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>WAS FAIL (both probes 400 FOREIGN KEY constraint failed). NOW PASS against a WAITER device enrolled after the fix. The earlier diagnosis is confirmed correct: the missing `device` row was the failing key, and minting it makes the identical request shape succeed.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>S-CUI-03</t>
+          <t>S-CAP-20</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2325,55 +2326,59 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Pairing the page with the REAL enrolled WAITER token reaches the Tables screen</t>
+          <t>A device paired BEFORE the fix stays permanently broken — the fix has no backfill</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>captain 9320 (Chromium 390×844)</t>
+          <t>captain 9320 -&gt; edge sqlite</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>WAITER device enrolled in the cloud at S-BE-06 (token 01a090d1…/len=80)</t>
+          <t>Two WAITER credentials at the same outlet: one cached before 758a70b (config_version 4), one enrolled after it (config_version 9). Same binary, same process, same request shape.</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Paste the real device token, tap Pair</t>
+          <t>POST /api/orders with the pre-fix device's token, immediately after the identical create succeeded on the post-fix device's token.</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Pair screen replaced by the Tables screen</t>
+          <t>If the fix repaired the outlet, both devices create. If it only repairs credentials that arrive in a bundle, the older device still fails.</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Paired; Tables screen shown</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Pre-fix device -&gt; HTTP 400 still "FOREIGN KEY constraint failed", while the post-fix device created successfully seconds earlier on the same process.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/captain-03-pair-real-token.png</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
+          <t>two creates seconds apart against holler-pos pid 55508, differing only in which WAITER credential authenticated; cloud device_credential.config_version 4 vs 9</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>MECHANISM. outlet.Repository.ListEdgeCredentials returns only credentials whose OWN config_version exceeds the edge's since_version cursor (backend/internal/outlet/device.go:154-164). A credential already pulled is never re-sent, so config::apply_bundle's new insert loop never sees it and never mints its device row. The fix is correct for every device enrolled from now on and cannot repair one paired earlier. DEMO RISK: re-pairing the same phone does NOT help — pairing re-uses the existing credential; the device must be re-ENROLLED to get a credential above the cursor.</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>WAS FAIL — 'That device token was rejected', the listener answering 401 'device credential not cached locally'. NOW PASS: the same token reaches the Tables screen. The credential is present at the edge now and was not before. THE AUTH PATH WAS NEVER BROKEN — the credential had simply not been pulled yet.</t>
+          <t>NEW ROW this run. Found while establishing why the fixed binary still refused the original paired device: the fix was verified working, and the failure that remained was a different one the fix does not cover.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>S-CUI-04</t>
+          <t>S-CUI-01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2383,7 +2388,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Tables screen lists the outlet's tables with free/occupied state</t>
+          <t>The captain page is served by the POS process and renders the pair screen at phone width</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2393,22 +2398,22 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Paired captain session</t>
+          <t>POS process hosts the captain listener and serves apps/captain/dist</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Read the table tiles</t>
+          <t>Navigate to http://localhost:9320/ in a 390px mobile context</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>At least one tile, each labelled Free or Occupied</t>
+          <t>200, 'Pair this phone' visible, no console errors</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2 table tiles rendered</t>
+          <t>HTTP 200; pair heading visible=true; console errors=0</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2418,20 +2423,20 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/captain-04-tables.png</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>WAS BLOCKED by S-CUI-03. NOW PASS — pairing succeeded, so the screen renders.</t>
-        </is>
-      </c>
+          <t>docs/demo-screens/scenarios/captain-01-pair.png</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Real listener, real bundle — nothing intercepted.</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>S-CUI-05</t>
+          <t>S-CUI-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2441,7 +2446,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Tapping a table opens the menu and cart screen</t>
+          <t>Pairing the page with a garbage token is refused and the bad token is not persisted</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2451,22 +2456,22 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Tables screen showing; tapping T1</t>
+          <t>Pair screen showing, localStorage empty</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Tap a table tile, wait for the menu list</t>
+          <t>Paste a fabricated credential_id.secret, tap Pair, then read localStorage</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>The menu list renders with the table name as the heading</t>
+          <t>A rejection message, and NOTHING stored — a mistyped token is never persisted as though it worked</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>2 menu rows under heading "T1"</t>
+          <t>message="That device token was rejected. Check it and paste it again."; localStorage token stored=false</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2476,20 +2481,20 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/captain-05-menu.png</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>WAS BLOCKED by S-CUI-03. NOW PASS — pairing succeeded, so the screen renders.</t>
-        </is>
-      </c>
+          <t>docs/demo-screens/scenarios/captain-02-garbage-token.png</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Falsifier for S-CUI-03: a page that stores whatever is typed would show a 'paired' state either way.</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>S-CUI-06</t>
+          <t>S-CUI-03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2499,7 +2504,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>A snoozed item is marked 'Not available' on the waiter's phone</t>
+          <t>Pairing the page with the REAL enrolled WAITER token reaches the Tables screen</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2509,49 +2514,45 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>At least one menu item with is_available = false</t>
+          <t>WAITER device enrolled in the cloud at S-BE-06 (token 01a09111…/len=80)</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Count .unavailable-tag elements on the menu screen</t>
+          <t>Paste the real device token, tap Pair</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>One per snoozed item; the page respects the field it is served</t>
+          <t>Pair screen replaced by the Tables screen</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>No item in this catalogue is snoozed, so the page's handling of is_available is UNEXERCISED by this run</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>NOT TESTABLE</t>
+          <t>Paired; Tables screen shown</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/captain-05-menu.png</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>Creating a stock-out to force this would need the till UI, which cannot be driven here. S-CAP-07 proves the field is SERVED; nothing in this run proves the page HONOURS it.</t>
-        </is>
-      </c>
+          <t>docs/demo-screens/scenarios/captain-03-pair-real-token.png</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>WAS BLOCKED by S-CUI-03. NOW NOT TESTABLE, which is a different thing and a weaker result than a pass: the screen renders, but no item in this catalogue is snoozed, so the page's is_available handling was never exercised. Recorded as unexercised rather than assumed working.</t>
+          <t>WAS FAIL — 'That device token was rejected', the listener answering 401 'device credential not cached locally'. NOW PASS: the same token reaches the Tables screen. The credential is present at the edge now and was not before. THE AUTH PATH WAS NEVER BROKEN — the credential had simply not been pulled yet.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>S-CUI-07</t>
+          <t>S-CUI-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2561,7 +2562,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Adding an item updates the cart bar count and total</t>
+          <t>Tables screen lists the outlet's tables with free/occupied state</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2571,22 +2572,22 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Menu screen showing with an empty cart</t>
+          <t>Paired captain session</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Tap the first menu row (confirming a modifier sheet if one opens), read the cart bar</t>
+          <t>Read the table tiles</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Count of 1 or more and a non-zero rupee total, formatted from integer paise</t>
+          <t>At least one tile, each labelled Free or Occupied</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>cart bar reads "1 item" / "₹55.00"</t>
+          <t>2 table tiles rendered</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2596,7 +2597,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/captain-06-cart.png</t>
+          <t>docs/demo-screens/scenarios/captain-04-tables.png</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr"/>
@@ -2609,7 +2610,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>S-CUI-08</t>
+          <t>S-CUI-05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2619,7 +2620,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Sending from the phone reaches the 'Sent to the kitchen' screen with the KOT list</t>
+          <t>Tapping a table opens the menu and cart screen</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2629,45 +2630,45 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Cart holding at least one line</t>
+          <t>Tables screen showing; tapping T1</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Tap Send, wait for the confirmation screen</t>
+          <t>Tap a table tile, wait for the menu list</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>'Sent to the kitchen' heading and at least one KOT row</t>
+          <t>The menu list renders with the table name as the heading</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Still on the cart. Error: "sqlite error: FOREIGN KEY constraint failed"</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>2 menu rows under heading "T1"</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/captain-07-sent.png</t>
+          <t>docs/demo-screens/scenarios/captain-05-menu.png</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>WAS BLOCKED by S-CUI-03 (no authenticated screen rendered). NOW FAIL on its own evidence, one step further on: the page reaches the cart and the send is refused with 'sqlite error: FOREIGN KEY constraint failed'. Root cause isolated in S-CAP-19.</t>
+          <t>WAS BLOCKED by S-CUI-03. NOW PASS — pairing succeeded, so the screen renders.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>S-KDS-02</t>
+          <t>S-CUI-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2677,90 +2678,94 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>THE CENTRAL CLAIM — a KOT sent from the waiter's phone reaches the KDS hub</t>
+          <t>A snoozed item is marked 'Not available' on the waiter's phone</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>captain 9320 -&gt; KDS LAN ws 9310</t>
+          <t>captain 9320 (Chromium 390×844)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>An order created and sent from the captain API</t>
+          <t>At least one menu item with is_available = false</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>n/a — no order can be created</t>
+          <t>Count .unavailable-tag elements on the menu screen</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>A kot_upserted frame naming a KOT id from the send response</t>
+          <t>One per snoozed item; the page respects the field it is served</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED by S-CAP-10. The demo's central claim cannot be exercised at all: the waiter's phone authenticates, lists tables, lists the menu, and then cannot create an order.</t>
+          <t>No item in this catalogue is snoozed, so the page's handling of is_available is UNEXERCISED by this run</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT TESTABLE</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>POST /api/orders -&gt; HTTP 400 STORAGE_ERROR</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+          <t>docs/demo-screens/scenarios/captain-05-menu.png</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Creating a stock-out to force this would need the till UI, which cannot be driven here. S-CAP-07 proves the field is SERVED; nothing in this run proves the page HONOURS it.</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>STILL BLOCKED, new reason: pairing now works, so the block moved from S-CUI-03 to the order-create foreign key in S-CAP-19.</t>
+          <t>WAS BLOCKED by S-CUI-03. NOW NOT TESTABLE, which is a different thing and a weaker result than a pass: the screen renders, but no item in this catalogue is snoozed, so the page's is_available handling was never exercised. Recorded as unexercised rather than assumed working.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>S-KDS-03</t>
+          <t>S-CUI-07</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1a / 3</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>The KDS loads past its config gate</t>
+          <t>Adding an item updates the cart bar count and total</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>KDS 5174 (Chromium)</t>
+          <t>captain 9320 (Chromium 390×844)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Vite dev server on 5174 started with --mode dev, so .env.dev supplies the LAN config</t>
+          <t>Menu screen showing with an empty cart</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Navigate to http://localhost:5174/, wait for mount</t>
+          <t>Tap the first menu row (confirming a modifier sheet if one opens), read the cart bar</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>'Kitchen Display' heading, and NO 'KDS is not configured' screen</t>
+          <t>Count of 1 or more and a non-zero rupee total, formatted from integer paise</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200; heading visible=true; config-error screens=0; console errors=0</t>
+          <t>cart bar reads "1 item" / "₹55.00"</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2770,55 +2775,55 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/kds-01-loaded.png</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>The config-error screen is the falsifier: a missing env var replaces the whole app with it.</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
+          <t>docs/demo-screens/scenarios/captain-06-cart.png</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>WAS BLOCKED by S-CUI-03. NOW PASS — pairing succeeded, so the screen renders.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>S-KDS-04</t>
+          <t>S-CUI-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1a / 3</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>The KDS connects to the real LAN socket hosted inside the POS process</t>
+          <t>Sending from the phone reaches the 'Sent to the kitchen' screen with the KOT list</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>KDS 5174 → ws 9310</t>
+          <t>captain 9320 (Chromium 390×844)</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>POS process bound on 9310; KDS device credential cached at the edge</t>
+          <t>Cart holding at least one line</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Poll [data-testid="connection-status"] for data-status="connected" for up to 10s</t>
+          <t>Tap Send, wait for the confirmation screen</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>data-status="connected" and no connection banner</t>
+          <t>'Sent to the kitchen' heading and at least one KOT row</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>data-status="connected"; banner=null</t>
+          <t>Sent screen shown with 1 KOT row(s)</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2828,237 +2833,237 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/kds-02-connected.png</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>The banner renders ONLY when not connected, so its absence is a second, independent signal.</t>
-        </is>
-      </c>
+          <t>docs/demo-screens/scenarios/captain-07-sent.png</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>WAS FAIL (data-status='disconnected'). NOW PASS — the socket is up because the POS process hosting it is up. The earlier failure was the dead process, not the KDS.</t>
+          <t>T30: WAS FAIL (the phone reached the cart and the send was refused with 'sqlite error: FOREIGN KEY constraint failed'). NOW PASS on the real phone screen — the send reaches the 'Sent to the kitchen' screen with its KOT list.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>S-KDS-05</t>
+          <t>S-KDS-01</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1a / 3</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>The KDS renders live tickets received in the snapshot</t>
+          <t>A second client can subscribe to the real KDS LAN socket and receives a snapshot</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>KDS 5174 → ws 9310</t>
+          <t>KDS LAN ws 9310</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>KOTs exist at the edge (the POS and S-CAP-14 have cut several this session)</t>
+          <t>POS process hosts the LAN server; KDS device credential from apps/kds/.env.dev (never printed)</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Wait up to 8s for article.ticket-card elements</t>
+          <t>Open ws://localhost:9310/kds?outlet_id&amp;device_id, send the first-frame auth message, await a snapshot frame</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>At least one ticket card carrying a data-kot-id</t>
+          <t>Socket opens, auth accepted, a snapshot frame arrives</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>No ticket cards; board says "No active tickets". The edge's own snapshot carried 0 ticket(s)</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>Socket open; snapshot received = true; snapshot tickets = 3; frames seen = 1</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/kds-03-tickets.png; edge snapshot ticket count = 0</t>
+          <t>snapshot frame with 3 tickets</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>NOT A KDS DEFECT. Subscribing to 9310 as a second client shows the EDGE puts zero tickets in the snapshot, so the board is showing exactly what it was sent. There is no active ticket at this outlet, and the two ways to create one are both unavailable here: the captain send fails on a foreign key (S-CAP-10) and the till UI is a native WebView2 that Playwright cannot drive. Read this row as 'the rendering path is unexercised', never as 'the KDS works' — an empty board is what a broken renderer looks like too, and this run cannot tell them apart.</t>
+          <t>Subscribed BEFORE the send, so a ticket observed in S-KDS-02 cannot be one that was already on the hub.</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>WAS FAIL (read as a KDS defect). NOW BLOCKED, and the demotion is the point: the edge's own snapshot carries 0 tickets, so there is nothing for the board to render and the KDS is behaving correctly. The board cannot be judged until S-CHAIN-02 can put a ticket on it.</t>
+          <t>T30: WAS NOT TESTABLE — 'apps/kds/.env.dev carries no VITE_KDS_DEVICE_TOKEN'. The file carried one all along. This stage split the file on "\n" and matched /^(VITE_[A-Z_]+)=(.*)$/, and `\r` is a LINE TERMINATOR in a JavaScript regex, so `.` never matched it, `$` never reached end-of-string, and every key silently failed to parse. NOW PASS.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>S-KDS-06</t>
+          <t>S-KDS-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Bumping a ticket advances its status on the board</t>
+          <t>THE CENTRAL CLAIM — a KOT sent from the waiter's phone reaches the KDS hub</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>KDS 5174 → ws 9310</t>
+          <t>captain 9320 → KDS LAN ws 9310</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>At least one ticket on the board</t>
+          <t>Socket subscribed and idle at 1 frames BEFORE the send; order 01a09114-08bd-7a73-9af1-ddd39e018190 not yet sent</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>POST /api/orders/{orderId}/send, then await a kot_upserted frame carrying one of the returned KOT ids</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>A kot_upserted frame naming a KOT id from the send response</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED by S-KDS-05: no ticket card is on the board to bump</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>kot_upserted received for KOT 01a09115-06ea-7d60-b1fa-e4440769c825; frames grew 1 → 3</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/kds-03-tickets.png</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr"/>
+          <t>kot_upserted frame, KOT 01a09115-06ea-7d60-b1fa-e4440769c825, order 01a09114-08bd-7a73-9af1-ddd39e018190</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>The frame count before the send is recorded so an arriving ticket cannot be confused with a ticket already on the hub.</t>
+        </is>
+      </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>STILL BLOCKED, new reason: not the dead POS but S-CHAIN-02 — no order can be created, so no ticket exists to bump.</t>
+          <t>T30: WAS BLOCKED, then FAIL on a socket this stage never actually opened. NOW PASS — kot_upserted received for a KOT cut by the waiter's phone. TWO separate causes were fixed to get here: 758a70b (the order could not be created at all) and this stage's own CRLF parse of apps/kds/.env.dev, which silently yielded no KDS device token and made the stage report a socket failure it had never attempted.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>S-KDS-07</t>
+          <t>S-KDS-03</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1a / 3</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>A bumped status survives a page reload, so it was persisted at the edge</t>
+          <t>The KDS loads past its config gate</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>KDS 5174 → ws 9310</t>
+          <t>KDS 5174 (Chromium)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>At least one ticket on the board</t>
+          <t>Vite dev server on 5174 started with --mode dev, so .env.dev supplies the LAN config</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Navigate to http://localhost:5174/, wait for mount</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>'Kitchen Display' heading, and NO 'KDS is not configured' screen</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED by S-KDS-05: no ticket card is on the board to bump</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>HTTP 200; heading visible=true; config-error screens=0; console errors=0</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/kds-03-tickets.png</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>STILL BLOCKED, new reason: not the dead POS but S-CHAIN-02 — no ticket exists to bump, so no bump can be reloaded.</t>
-        </is>
-      </c>
+          <t>docs/demo-screens/scenarios/kds-01-loaded.png</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>The config-error screen is the falsifier: a missing env var replaces the whole app with it.</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-01</t>
+          <t>S-KDS-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1a / 3</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>The admin console loads and shows its sign-in form</t>
+          <t>The KDS connects to the real LAN socket hosted inside the POS process</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>admin 5175</t>
+          <t>KDS 5174 → ws 9310</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Vite dev server on 5175; VITE_ADMIN_API_BASE_URL=http://localhost:8080 in apps/admin/.env.local</t>
+          <t>POS process bound on 9310; KDS device credential cached at the edge</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Navigate to http://localhost:5175/</t>
+          <t>Poll [data-testid="connection-status"] for data-status="connected" for up to 10s</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>200, a 'Sign in' heading, and no 'VITE_… is not set' env error</t>
+          <t>data-status="connected" and no connection banner</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200; Sign in heading=true; env-error blocks=0; console errors=0</t>
+          <t>data-status="connected"; banner=null</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -3068,51 +3073,59 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/admin-01-signin.png</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
+          <t>docs/demo-screens/scenarios/kds-02-connected.png</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>The banner renders ONLY when not connected, so its absence is a second, independent signal.</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>WAS FAIL (data-status='disconnected'). NOW PASS — the socket is up because the POS process hosting it is up. The earlier failure was the dead process, not the KDS.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-02</t>
+          <t>S-KDS-05</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1a / 3</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Sign in to the admin console with real credentials against the live backend</t>
+          <t>The KDS renders live tickets received in the snapshot</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>admin 5175 → backend 8080</t>
+          <t>KDS 5174 → ws 9310</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>owner@holler.test exists; login budget not exhausted for this IP</t>
+          <t>KOTs exist at the edge (the POS and S-CAP-14 have cut several this session)</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Fill Email and Password, click Sign in (ONE attempt — the endpoint allows five per fifteen minutes per IP)</t>
+          <t>Wait up to 8s for article.ticket-card elements</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>The tab bar and the Menu and pricing screen replace the form</t>
+          <t>At least one ticket card carrying a data-kot-id</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Signed in; Menu and pricing screen shown</t>
+          <t>5 ticket cards rendered, and the edge's own snapshot carried 5</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -3122,59 +3135,55 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/admin-02-after-signin.png</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>Session is in-memory only: any reload returns to Sign in, which costs another attempt against the budget.</t>
-        </is>
-      </c>
+          <t>docs/demo-screens/scenarios/kds-03-tickets.png; edge snapshot ticket count = 5</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>WAS FAIL ('Sign-in failed…'). NOW PASS with unchanged credentials — the earlier failure was the shared login rate-limit budget, indistinguishable by design from a wrong password (S-BE-09). Nothing was reconfigured; the window rolled.</t>
+          <t>T30: WAS BLOCKED (the edge's own snapshot carried 0 tickets, so there was nothing for the board to render and the KDS was behaving correctly). NOW PASS — 5 ticket cards rendered against an edge snapshot carrying 5. The rendering path is exercised for the first time, because the order-create foreign key no longer stops a ticket existing.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-03</t>
+          <t>S-KDS-06</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Menu and pricing loads real rows from the live backend</t>
+          <t>Bumping a ticket advances its status, echoed back by the edge</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>admin 5175 → backend 8080</t>
+          <t>KDS 5174 → ws 9310 → POS</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Signed in; the cloud holds 43 menu_item rows</t>
+          <t>Ticket 01a09112-3c38-7f91-a801-3f4ce1ffef43 showing status "New" with a "Accept" button</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Read the menu table rows</t>
+          <t>Click button.ticket-card__advance, then poll the SAME card's .ticket-card__status until it changes</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>A populated table, not a loading or empty state</t>
+          <t>The card's status text changes — proof the edge accepted and echoed set_kot_status</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>44 table rows (including the header); 'Loading menu…' present=false</t>
+          <t>"New" → "Accepted" after clicking "Accept"</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -3184,55 +3193,59 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/admin-03-menu.png</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+          <t>docs/demo-screens/scenarios/kds-04-bumped.png</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Asserted on the card, never on the click: the KDS is not authoritative and repaints only after the edge echoes kot_upserted, so a click that changed nothing would still look like a click.</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>WAS BLOCKED by S-ADM-02. NOW PASS — sign-in succeeded, so the screen loads real rows.</t>
+          <t>T30: WAS BLOCKED (no ticket existed to bump). NOW PASS — a ticket advanced "New" → "Accepted", asserted on the card after the edge echoed kot_upserted, never on the click.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-04</t>
+          <t>S-KDS-07</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>A price edit persists through the backend, not just in the screen's cache</t>
+          <t>The bumped status survived a reload, so it was persisted at the edge and not held in page state</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>admin 5175 → backend 8080 → postgres</t>
+          <t>KDS 5174 → ws 9310</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Menu and pricing loaded with at least one editable row</t>
+          <t>Ticket 01a09112-3c38-7f91-a801-3f4ce1ffef43 bumped from "New" to "Accepted" in S-KDS-06</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Edit, bump the price by ₹1, Save, navigate away to Suppliers and back, re-read the row</t>
+          <t>Reload the page, let the fresh snapshot arrive, read the same card's status</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>The re-read row shows the new price — proof it went through PATCH /menu/items/{itemId}</t>
+          <t>The same card still reads "Accepted" — the snapshot is rebuilt from the edge, not from the browser</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Edited 121.00 → 122.00; save error=null; after leaving and re-entering the screen the row reads 122.00 (persisted)</t>
+          <t>After reload the card reads "Accepted"</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -3242,24 +3255,24 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/admin-04-price-edit.png</t>
+          <t>docs/demo-screens/scenarios/kds-05-after-reload.png</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>The navigate-away-and-back is the falsifier: a screen that only mutated local state would show the new price until something re-fetched, and the naive assertion would pass.</t>
+          <t>A reload discards all page state, so a status still showing after it came from the edge's snapshot.</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>WAS BLOCKED by S-ADM-02. NOW PASS — a price edit was written and read back from the backend.</t>
+          <t>T30: WAS BLOCKED (no bump to reload). NOW PASS — after a full page reload the same card still reads "Accepted", so the bump was persisted at the edge and not held in page state.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-05</t>
+          <t>S-ADM-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3269,32 +3282,32 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Suppliers and pack sizes loads from the live backend</t>
+          <t>The admin console loads and shows its sign-in form</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>admin 5175 → backend 8080</t>
+          <t>admin 5175</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Signed in</t>
+          <t>Vite dev server on 5175; VITE_ADMIN_API_BASE_URL=http://localhost:8080 in apps/admin/.env.local</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Click the Suppliers tab, wait for the query to settle</t>
+          <t>Navigate to http://localhost:5175/</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>The heading renders and the screen shows suppliers or its empty state, with no error</t>
+          <t>200, a 'Sign in' heading, and no 'VITE_… is not set' env error</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>heading=true; supplier cards=1; empty state shown=false; error=null</t>
+          <t>HTTP 200; Sign in heading=true; env-error blocks=0; console errors=0</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -3304,30 +3317,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/admin-05-suppliers.png</t>
+          <t>docs/demo-screens/scenarios/admin-01-signin.png</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>WAS BLOCKED by S-ADM-02. NOW PASS — sign-in succeeded, so the screen loads.</t>
-        </is>
-      </c>
+      <c r="L48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-06</t>
+          <t>S-ADM-02</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Goods receipts loads and is labelled as the replica it is</t>
+          <t>Sign in to the admin console with real credentials against the live backend</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3337,22 +3346,22 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Signed in; a GRN is edge-authoritative and the cloud holds a copy (ADR-019)</t>
+          <t>owner@holler.test exists; login budget not exhausted for this IP</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Click the Goods receipts tab, wait for the query to settle</t>
+          <t>Fill Email and Password, click Sign in (ONE attempt — the endpoint allows five per fifteen minutes per IP)</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>The heading renders; receipts or the empty state, no error</t>
+          <t>The tab bar and the Menu and pricing screen replace the form</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>heading=true; GRN cards=1; empty state shown=false; error=null</t>
+          <t>Signed in; Menu and pricing screen shown</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -3362,24 +3371,24 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/admin-06-goods-receipts.png</t>
+          <t>docs/demo-screens/scenarios/admin-02-after-signin.png</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>GET /procurement/goods-receipts serves a REPLICA and every surface must label it as one (contracts 0.7.0).</t>
+          <t>Session is in-memory only: any reload returns to Sign in, which costs another attempt against the budget.</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>WAS BLOCKED by S-ADM-02. NOW PASS — sign-in succeeded, so the screen loads.</t>
+          <t>WAS FAIL ('Sign-in failed…'). NOW PASS with unchanged credentials — the earlier failure was the shared login rate-limit budget, indistinguishable by design from a wrong password (S-BE-09). Nothing was reconfigured; the window rolled.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-07</t>
+          <t>S-ADM-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3389,32 +3398,32 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>No raw UUID is shown to a human on any admin screen</t>
+          <t>Menu and pricing loads real rows from the live backend</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>admin 5175</t>
+          <t>admin 5175 → backend 8080</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>All three tabs reachable</t>
+          <t>Signed in; the cloud holds 43 menu_item rows</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Read the rendered text of each tab and match the UUID pattern</t>
+          <t>Read the menu table rows</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>0 — human-facing identifiers are short (Order #A184, GRN/20260902), never a primary key</t>
+          <t>A populated table, not a loading or empty state</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Distinct UUIDs visible per tab: Menu and pricing=0, Suppliers=0, Goods receipts=0</t>
+          <t>44 table rows (including the header); 'Loading menu…' present=false</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -3424,171 +3433,175 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/admin-07-uuid-scan.png</t>
+          <t>docs/demo-screens/scenarios/admin-03-menu.png</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr"/>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>WAS BLOCKED by S-ADM-02. NOW PASS — sign-in succeeded, so the screen could be inspected.</t>
+          <t>WAS BLOCKED by S-ADM-02. NOW PASS — sign-in succeeded, so the screen loads real rows.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-08</t>
+          <t>S-ADM-04</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Orders screen</t>
+          <t>A price edit persists through the backend, not just in the screen's cache</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>admin 5175</t>
+          <t>admin 5175 → backend 8080 → postgres</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>The admin console signed in</t>
+          <t>Menu and pricing loaded with at least one editable row</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Enumerate apps/admin/src/components and the tab bar for the screen</t>
+          <t>Edit, bump the price by ₹1, Save, navigate away to Suppliers and back, re-read the row</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>A orders screen screen the demo can show</t>
+          <t>The re-read row shows the new price — proof it went through PATCH /menu/items/{itemId}</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>NOT BUILT. The admin console has three tabs — Menu and pricing, Suppliers, Goods receipts. There is no orders screen, no order route in apps/admin/src/lib/api.ts, and no component for one. Demo step 4 has no surface.</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Edited 121.00 → 122.00; save error=null; after leaving and re-entering the screen the row reads 122.00 (persisted)</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>apps/admin/src/components contains exactly SignIn.tsx, MenuScreen.tsx, SuppliersScreen.tsx, GoodsReceiptsScreen.tsx; apps/admin/src/lib/api.ts exposes only menu, supplier and goods-receipt endpoints</t>
+          <t>docs/demo-screens/scenarios/admin-04-price-edit.png</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>KNOWN ABSENT — recorded as FAIL rather than skipped, because the demo script names this step.</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr"/>
+          <t>The navigate-away-and-back is the falsifier: a screen that only mutated local state would show the new price until something re-fetched, and the naive assertion would pass.</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>WAS BLOCKED by S-ADM-02. NOW PASS — a price edit was written and read back from the backend.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>S-ADM-09</t>
+          <t>S-ADM-05</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Stock variance screen</t>
+          <t>Suppliers and pack sizes loads from the live backend</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>admin 5175</t>
+          <t>admin 5175 → backend 8080</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>The admin console signed in</t>
+          <t>Signed in</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Enumerate apps/admin/src/components and the tab bar for the screen</t>
+          <t>Click the Suppliers tab, wait for the query to settle</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>A stock variance screen screen the demo can show</t>
+          <t>The heading renders and the screen shows suppliers or its empty state, with no error</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>NOT BUILT. No stock, variance or count screen exists in the admin console and no inventory endpoint is wired into apps/admin/src/lib/api.ts. Demo step 5 has no surface — and gap A7 means the underlying stock_count rows never reach the cloud either (S-SYNC-04), so the data is absent as well as the screen.</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>heading=true; supplier cards=1; empty state shown=false; error=null</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>apps/admin/src/components contains exactly SignIn.tsx, MenuScreen.tsx, SuppliersScreen.tsx, GoodsReceiptsScreen.tsx; apps/admin/src/lib/api.ts exposes only menu, supplier and goods-receipt endpoints</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>KNOWN ABSENT — recorded as FAIL rather than skipped, because the demo script names this step.</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr"/>
+          <t>docs/demo-screens/scenarios/admin-05-suppliers.png</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>WAS BLOCKED by S-ADM-02. NOW PASS — sign-in succeeded, so the screen loads.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>S-API-01</t>
+          <t>S-ADM-06</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>PATCH /menu/items/{itemId} changes a price and it lands in Postgres</t>
+          <t>Goods receipts loads and is labelled as the replica it is</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>backend 8080 -&gt; postgres 5432</t>
+          <t>admin 5175 → backend 8080</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Menu item "Aloo Tikki Chaat" at 12300 paise</t>
+          <t>Signed in; a GRN is edge-authoritative and the cloud holds a copy (ADR-019)</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>PATCH base_price_paise +100, then read the column back from Postgres</t>
+          <t>Click the Goods receipts tab, wait for the query to settle</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2xx and the stored column reading 12400</t>
+          <t>The heading renders; receipts or the empty state, no error</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200; stored base_price_paise=12400</t>
+          <t>heading=true; GRN cards=1; empty state shown=false; error=null</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -3598,20 +3611,24 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200; SQL base_price_paise=12400</t>
+          <t>docs/demo-screens/scenarios/admin-06-goods-receipts.png</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>Read back from the database, not from the response echo — an echo cannot see a write that did not happen.</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr"/>
+          <t>GET /procurement/goods-receipts serves a REPLICA and every surface must label it as one (contracts 0.7.0).</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>WAS BLOCKED by S-ADM-02. NOW PASS — sign-in succeeded, so the screen loads.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>S-API-02</t>
+          <t>S-ADM-07</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3621,105 +3638,105 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>PATCH /menu/items/{itemId} refuses an identity field rather than ignoring it</t>
+          <t>No raw UUID is shown to a human on any admin screen</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>backend 8080</t>
+          <t>admin 5175</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>A valid owner JWT and a real menu item</t>
+          <t>All three tabs reachable</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>PATCH with an `id` field in the body</t>
+          <t>Read the rendered text of each tab and match the UUID pattern</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>422 — id/outlet_id/tenant_id are 422 if present, never a silent ignore (contracts 0.7.0)</t>
+          <t>0 — human-facing identifiers are short (Order #A184, GRN/20260902), never a primary key</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400 invalid_input</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Distinct UUIDs visible per tab: Menu and pricing=0, Suppliers=0, Goods receipts=0</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400 invalid_input</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>LOW SEVERITY, AND THE LOAD-BEARING HALF IS CORRECT. The requirement contracts 0.7.0 actually cares about is 'never a silent ignore', and the route does reject — it answers 400 invalid_input, which is the shared DisallowUnknownFields decoder refusing the field before the handler sees it. What deviates is only the status code: the contract says 422, the route says 400. Recorded as FAIL because the edge classifier branches on these values and contracts 0.7.0 made ErrorCode an enum precisely so a status or code drifting from the spec is not a silent behaviour change — but nothing about this is visible to the demo.</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr"/>
+          <t>docs/demo-screens/scenarios/admin-07-uuid-scan.png</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>WAS BLOCKED by S-ADM-02. NOW PASS — sign-in succeeded, so the screen could be inspected.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>S-API-03</t>
+          <t>S-ADM-08</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>PATCH /menu/items/{itemId} may change hsn_sac but never clear it</t>
+          <t>Orders screen</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>backend 8080 -&gt; postgres 5432</t>
+          <t>admin 5175</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Item "Aloo Tikki Chaat" carrying hsn_sac "9963"</t>
+          <t>The admin console signed in</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>PATCH hsn_sac to an empty string, then read the column back</t>
+          <t>Enumerate apps/admin/src/components and the tab bar for the screen</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>4xx, and the stored value unchanged — an invoice cannot issue without HSN/SAC (contracts 0.4.5)</t>
+          <t>A orders screen screen the demo can show</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400; stored hsn_sac now "9963" (was "9963")</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>NOT BUILT. The admin console has three tabs — Menu and pricing, Suppliers, Goods receipts. There is no orders screen, no order route in apps/admin/src/lib/api.ts, and no component for one. Demo step 4 has no surface.</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>HTTP 400; SQL hsn_sac=9963</t>
+          <t>apps/admin/src/components contains exactly SignIn.tsx, MenuScreen.tsx, SuppliersScreen.tsx, GoodsReceiptsScreen.tsx; apps/admin/src/lib/api.ts exposes only menu, supplier and goods-receipt endpoints</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>The read-back is the real assertion: a 4xx with the column cleared anyway would still be a defect.</t>
+          <t>KNOWN ABSENT — recorded as FAIL rather than skipped, because the demo script names this step.</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr"/>
@@ -3727,57 +3744,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>S-API-04</t>
+          <t>S-ADM-09</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>GET /procurement/goods-receipts serves the cloud replica of edge-authoritative receipts</t>
+          <t>Stock variance screen</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>backend 8080 -&gt; postgres 5432</t>
+          <t>admin 5175</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Postgres holds 1 goods_receipt_note row(s)</t>
+          <t>The admin console signed in</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>GET /procurement/goods-receipts for this outlet and compare the count with the table</t>
+          <t>Enumerate apps/admin/src/components and the tab bar for the screen</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2xx returning 1 receipt(s), each carrying all three quantity fields</t>
+          <t>A stock variance screen screen the demo can show</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200; 1 receipt(s) returned against 1 row(s) in goods_receipt_note. Body keys: items,next_cursor</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>NOT BUILT. No stock, variance or count screen exists in the admin console and no inventory endpoint is wired into apps/admin/src/lib/api.ts. Demo step 5 has no surface — and gap A7 means the underlying stock_count rows never reach the cloud either (S-SYNC-04), so the data is absent as well as the screen.</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200; API 1 vs SQL 1</t>
+          <t>apps/admin/src/components contains exactly SignIn.tsx, MenuScreen.tsx, SuppliersScreen.tsx, GoodsReceiptsScreen.tsx; apps/admin/src/lib/api.ts exposes only menu, supplier and goods-receipt endpoints</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>A GRN is edge-authoritative and this is a REPLICA — the outlet's own view may legitimately differ and the two are shown and labelled, never reconciled (contracts 0.7.0). An empty result here is consistent with gap A7: if no receipt has ever replayed, the correct answer IS zero, and the count comparison says which case this is.</t>
+          <t>KNOWN ABSENT — recorded as FAIL rather than skipped, because the demo script names this step.</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr"/>
@@ -3785,42 +3802,42 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-01</t>
+          <t>S-API-01</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Orders replay from the edge to the cloud at all</t>
+          <t>PATCH /menu/items/{itemId} changes a price and it lands in Postgres</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>postgres 5432</t>
+          <t>backend 8080 -&gt; postgres 5432</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>The outbox pump has run at least once since the POS started</t>
+          <t>Menu item "Aloo Tikki Chaat" at 12300 paise</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>select count(*) from "order" and order_item</t>
+          <t>PATCH base_price_paise +100, then read the column back from Postgres</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Non-zero — `order` is one of the two aggregates with an edge route (gap A7)</t>
+          <t>2xx and the stored column reading 12400</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>4 order rows, 2 order_item rows in the cloud</t>
+          <t>HTTP 200; stored base_price_paise=12400</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3830,124 +3847,128 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>SQL count(order)=4, count(order_item)=2</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr"/>
+          <t>HTTP 200; SQL base_price_paise=12400</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Read back from the database, not from the response echo — an echo cannot see a write that did not happen.</t>
+        </is>
+      </c>
       <c r="L57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-02</t>
+          <t>S-API-02</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1a / 6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>The order this run created from the captain page reaches Postgres</t>
+          <t>PATCH /menu/items/{itemId} refuses an identity field rather than ignoring it</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>captain 9320 → backend 8080 → postgres 5432</t>
+          <t>backend 8080</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>No captain order was created (S-CAP-10 did not run)</t>
+          <t>A valid owner JWT and a real menu item</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>select count(*) from "order" where id = &lt;the captain order id&gt;</t>
+          <t>PATCH with an `id` field in the body</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1 row</t>
+          <t>422 — id/outlet_id/tenant_id are 422 if present, never a silent ignore (contracts 0.7.0)</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>No captain order id available — S-CAP-10 was blocked</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>HTTP 400 invalid_input</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>S-CAP-10 blocked</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr"/>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>STILL BLOCKED, new reason: not 'S-CAP-10 was blocked' by a dead process but the order-create foreign key of S-CAP-19. No captain order exists to look for in Postgres.</t>
-        </is>
-      </c>
+          <t>HTTP 400 invalid_input</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>LOW SEVERITY, AND THE LOAD-BEARING HALF IS CORRECT. The requirement contracts 0.7.0 actually cares about is 'never a silent ignore', and the route does reject — it answers 400 invalid_input, which is the shared DisallowUnknownFields decoder refusing the field before the handler sees it. What deviates is only the status code: the contract says 422, the route says 400. Recorded as FAIL because the edge classifier branches on these values and contracts 0.7.0 made ErrorCode an enum precisely so a status or code drifting from the spec is not a silent behaviour change — but nothing about this is visible to the demo.</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-03</t>
+          <t>S-API-03</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>A replayed order's device_id resolves to a real device row in the cloud</t>
+          <t>PATCH /menu/items/{itemId} may change hsn_sac but never clear it</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>postgres 5432</t>
+          <t>backend 8080 -&gt; postgres 5432</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Orders present in the cloud</t>
+          <t>Item "Aloo Tikki Chaat" carrying hsn_sac "9963"</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Left join "order".device_id to device.id and report the kind</t>
+          <t>PATCH hsn_sac to an empty string, then read the column back</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Every order's device_id joins to a device row, so attribution is readable in the back office</t>
+          <t>4xx, and the stored value unchanged — an invoice cannot issue without HSN/SAC (contracts 0.4.5)</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Across all orders: &lt;no device row&gt; x4</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>HTTP 400; stored hsn_sac now "9963" (was "9963")</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>SQL: &lt;no device row&gt; x4</t>
+          <t>HTTP 400; SQL hsn_sac=9963</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>Every order currently replays with device_id 0191a000-0000-7000-8000-00000000000b, a seed constant with NO row in the cloud `device` table (device ids there are 01a0908b-…). There is no FK from "order" to device, so the orphan replays silently. Waiter-versus-till attribution — the whole point of demo step 1a — is therefore not answerable from the cloud copy at all: both devices resolve to the same non-existent id.</t>
+          <t>The read-back is the real assertion: a 4xx with the column cleared anyway would still be a defect.</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr"/>
@@ -3955,57 +3976,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-04</t>
+          <t>S-API-04</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>4 / 5 / 6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>KNOWN GAP A7 — aggregates other than `order` never reach the cloud</t>
+          <t>GET /procurement/goods-receipts serves the cloud replica of edge-authoritative receipts</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>postgres 5432</t>
+          <t>backend 8080 -&gt; postgres 5432</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>The POS has been cutting KOTs all session; S-CAP-14 cut more this run</t>
+          <t>Postgres holds 1 goods_receipt_note row(s)</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Count each edge-authoritative aggregate in Postgres</t>
+          <t>GET /procurement/goods-receipts for this outlet and compare the count with the table</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>If A7 were closed: non-zero kot / invoice / payment / stock_count. As shipped: zero, because edge/sync/src/route.rs maps only `order` and `table_session`</t>
+          <t>2xx returning 1 receipt(s), each carrying all three quantity fields</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>kot=0, invoice=0, payment=0, stock_count=0, stock_ledger_entry=39, cash_shift=0, table_session=0</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>HTTP 200; 1 receipt(s) returned against 1 row(s) in goods_receipt_note. Body keys: items,next_cursor</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>SQL counts — kot=0, invoice=0, payment=0, stock_count=0, stock_ledger_entry=39, cash_shift=0, table_session=0</t>
+          <t>HTTP 200; API 1 vs SQL 1</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>KNOWN AND FILED. Gap A7 is carried out of M6 Phase A in docs/backlog.md with the trigger 'before the first pilot'. The cloud ingest routes exist; the EDGE RESOLVER does not, so the rows sit in the local outbox with no route. Recorded as FAIL, not skipped: the back-office demo steps 4 and 5 are built on data that cannot arrive. The KOT the KDS displayed in S-KDS-02 is real and LAN-local; it is simply invisible to the cloud.</t>
+          <t>A GRN is edge-authoritative and this is a REPLICA — the outlet's own view may legitimately differ and the two are shown and labelled, never reconciled (contracts 0.7.0). An empty result here is consistent with gap A7: if no receipt has ever replayed, the correct answer IS zero, and the count comparison says which case this is.</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr"/>
@@ -4013,17 +4034,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-05</t>
+          <t>S-SYNC-01</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>No unresolved cloud-side replay holes are recorded</t>
+          <t>Orders replay from the edge to the cloud at all</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4033,22 +4054,22 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>ledger_replay_gap records a ranged-stream hole; resolved_at clears it</t>
+          <t>The outbox pump has run at least once since the POS started</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>select count(*) from ledger_replay_gap</t>
+          <t>select count(*) from "order" and order_item</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>0, or every row carrying a resolved_at</t>
+          <t>Non-zero — `order` is one of the two aggregates with an edge route (gap A7)</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>ledger_replay_gap rows = 0</t>
+          <t>24 order rows, 8 order_item rows in the cloud</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -4058,88 +4079,84 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>SQL count(ledger_replay_gap) = 0</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>Vacuously clean while A7 keeps the stock streams from replaying at all — a zero here is not evidence the mechanism works.</t>
-        </is>
-      </c>
+          <t>SQL count(order)=24, count(order_item)=8</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-06</t>
+          <t>S-SYNC-02</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1a / 6</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Inspect the edge-local outbox (local_outbox, sync_replay_block) for stranded rows</t>
+          <t>The order this run created from the captain page reaches Postgres</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>edge SQLite</t>
+          <t>captain 9320 → backend 8080 → postgres 5432</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>The edge database file is encrypted at rest (ADR-011) and this suite must not copy or decrypt it</t>
+          <t>Captain created order 01a09114-08bd-7a73-9af1-ddd39e018190</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Would be: select from local_outbox / sync_replay_block on the edge SQLite file</t>
+          <t>select count(*) from "order" where id = &lt;the captain order id&gt;</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>A count of pending and permanently-blocked rows</t>
+          <t>1 row</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>NOT TESTABLE from outside the POS process. The edge SQLite file is encrypted at rest and there is no read surface for the outbox — no Tauri command, no captain route and no LAN frame exposes it</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>NOT TESTABLE</t>
+          <t>count=1 for order 01a09114-08bd-7a73-9af1-ddd39e018190</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>ADR-011: 'the edge SQLite file is encrypted at rest — never copy it or its backups anywhere unencrypted'</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>This is gap A3's surfacing half seen from the outside: a stranded row is visible only on the POS window, which cannot be driven here. The cloud-side consequence is measurable and IS measured in S-SYNC-04.</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr"/>
+          <t>SQL count=1</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>T30: WAS BLOCKED (no captain order existed to look for in Postgres). NOW PASS — the order this run created from the captain page is in the cloud "order" table.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-07</t>
+          <t>S-SYNC-03</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>The cloud menu is seeded, so an admin price edit has something to edit</t>
+          <t>A newly created order replays with a device_id that resolves to a real device row in the cloud</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4149,22 +4166,22 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>M6 C7 closed the cloud/edge seed drift as no longer needed</t>
+          <t>Captain order 01a09114-08bd-7a73-9af1-ddd39e018190 created this run and replayed</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>select count(*) from menu_item</t>
+          <t>Left join "order".device_id to device.id for the order THIS run created, and report the kind; then count every order in the cloud that still fails to resolve.</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Non-zero and comparable to the edge's 43</t>
+          <t>The order created this run joins to a device row of kind WAITER</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>43 menu_item rows in the cloud</t>
+          <t>Captain order 01a09114-08bd-7a73-9af1-ddd39e018190: WAITER|01a09111-126f-7e32-9f4d-6f35b064cb14. Across all orders: WAITER x20; &lt;no device row&gt; x4.</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -4174,26 +4191,34 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>SQL count(menu_item) = 43</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
+          <t>SQL left join "order" -&gt; device; WAITER x20; &lt;no device row&gt; x4</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>A SEPARATE, OPPOSITE GAP REMAINS AND IS NOT FIXED BY 758a70b — see S-SYNC-13. 4 order(s) still fail to resolve, every one of them carrying device_id 0191a000-0000-7000-8000-00000000000b, which is edge/database/src/bin/devseed.rs:41's DEVICE_ID — the TILL. That row is written locally by devseed and was never enrolled in the cloud, so Postgres has no `device` row for it. Note the direction: T30 fixed cloud→edge (a cloud-enrolled device missing its edge row); this is edge→cloud (an edge-seeded device missing its cloud row). There is no FK from "order" to device in Postgres, so the orphan replays silently.</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>WAS FAIL — no order in the cloud resolved to a device row, so waiter-versus-till attribution was unanswerable. NOW PASS for the order this run created: it resolves to a WAITER device. Re-scoped to the order under test because the rows that still fail are legacy till-authored ones a config-pull fix cannot reach; they are carried as S-SYNC-13 rather than left averaged into this verdict.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-08</t>
+          <t>S-SYNC-04</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>4 / 5 / 6</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Cloud variant coverage matches the edge, so a replayed order item does not violate its FK</t>
+          <t>KNOWN GAP A7 — aggregates other than `order` never reach the cloud</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4203,22 +4228,22 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>M6 C3 found order_item_variant_id_fkey, not the menu_item seed, was the real refusal key</t>
+          <t>The POS has been cutting KOTs all session; S-CAP-14 cut more this run</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Histogram of variants per menu_item in the cloud</t>
+          <t>Count each edge-authoritative aggregate in Postgres</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Every item carrying at least the variants the edge offers</t>
+          <t>If A7 were closed: non-zero kot / invoice / payment / stock_count. As shipped: zero, because edge/sync/src/route.rs maps only `order` and `table_session`</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>variants-per-item histogram (variants|items): 0|12, 1|9, 2|22</t>
+          <t>kot=0, invoice=0, payment=0, stock_count=0, stock_ledger_entry=39, cash_shift=0, table_session=0</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -4228,12 +4253,12 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>SQL histogram: 0|12 ; 1|9 ; 2|22</t>
+          <t>SQL counts — kot=0, invoice=0, payment=0, stock_count=0, stock_ledger_entry=39, cash_shift=0, table_session=0</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>docs/backlog.md records every ItemAdded being refused on the variant foreign key. Items with zero cloud variants are the rows that cannot accept a replayed line.</t>
+          <t>KNOWN AND FILED. Gap A7 is carried out of M6 Phase A in docs/backlog.md with the trigger 'before the first pilot'. The cloud ingest routes exist; the EDGE RESOLVER does not, so the rows sit in the local outbox with no route. Recorded as FAIL, not skipped: the back-office demo steps 4 and 5 are built on data that cannot arrive. The KOT the KDS displayed in S-KDS-02 is real and LAN-local; it is simply invisible to the cloud.</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr"/>
@@ -4241,42 +4266,42 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-09</t>
+          <t>S-SYNC-05</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1a / 6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>The periodic sync pump contacts the cloud at its documented interval</t>
+          <t>No unresolved cloud-side replay holes are recorded</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>POS process -&gt; backend 8080 -&gt; postgres 5432</t>
+          <t>postgres 5432</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>A5 landed a timer calling AppState::drain_outbox; DEFAULT_PERIODIC_DRAIN_INTERVAL is 60s (apps/pos/src-tauri/src/state.rs:93) and apps/pos/.env.dev sets no HOLLER_PERIODIC_DRAIN_INTERVAL_SECS override. The config pull runs FIRST on every tick, inside the same lock as the pump (ADR-024).</t>
+          <t>ledger_replay_gap records a ranged-stream hole; resolved_at clears it</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Sample device_credential.last_used_at for the POS device every 30s across a 7-minute window and measure the interval between distinct cloud contacts</t>
+          <t>select count(*) from ledger_replay_gap</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Contact at least every 60s, so a newly enrolled device is usable within a minute</t>
+          <t>0, or every row carrying a resolved_at</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Over 7 minutes of sampling the POS made 7 distinct cloud contact(s): 2026-09-11 14:32:37.575702+00 then 2026-09-11 14:33:37.906337+00 then 2026-09-11 14:34:38.252692+00 then 2026-09-11 14:35:38.635026+00 then 2026-09-11 14:36:38.957719+00 then 2026-09-11 14:37:39.264323+00 then 2026-09-11 14:38:39.586467+00. Longest observed gap between contacts: 1m0s against a documented 60s.</t>
+          <t>ledger_replay_gap rows = 0</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -4286,24 +4311,20 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/pos-uplink-watch-instance-80612-healthy.txt — 14 samples, window 2026-09-11 14:32:58.460877+00 to 2026-09-11 14:39:30.022613+00</t>
+          <t>SQL count(ledger_replay_gap) = 0</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>MEASURED ON A PROCESS WATCHED STAYING UP THROUGHOUT, which is what makes the number mean anything: across a process start and a process stop, the startup drain and the shutdown drain are indistinguishable from periodic ticks, and a first attempt at this measurement spanned exactly that and had to be thrown away. See S-SYNC-12 for what that first attempt DID find, which is a different defect and a real one.</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>WAS FAIL — 2 contacts in 6 minutes, longest gap 12m27s against a documented 60s, with the shutdown-drain alternative explicitly NOT excluded. NOW PASS: 7 contacts in 7 minutes, every gap 1m0s, measured on Postgres's clock. VERDICT ON STARTUP-PULL VERSUS PERIODIC-PULL: THE A5 PERIODIC PUMP IS NOT DEFECTIVE. It ticks at its documented interval on a healthy process. The earlier 12m27s gap belonged to the PREVIOUS process, which stopped pumping and then died minutes later — an instance that was already failing, not a design fault. So the pairing delay was a property of that sick process, not of the pump. NOTE WHAT THIS RUN DOES NOT SHOW: stage 01 REUSED the existing enrolment rather than minting a new credential, so no credential arrived from 401 to 200 during this run and the periodic pull was never watched delivering one. That it does is inferred from the proven 60s tick plus edge/sync/src/config.rs:770, not observed.</t>
-        </is>
-      </c>
+          <t>Vacuously clean while A7 keeps the stock streams from replaying at all — a zero here is not evidence the mechanism works.</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-10</t>
+          <t>S-SYNC-06</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4313,47 +4334,47 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>A replayed order carries its line items, not just its total</t>
+          <t>Inspect the edge-local outbox (local_outbox, sync_replay_block) for stranded rows</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>postgres 5432</t>
+          <t>edge SQLite</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Orders have replayed (S-SYNC-01) and the cloud holds menu_item_variant rows</t>
+          <t>The edge database file is encrypted at rest (ADR-011) and this suite must not copy or decrypt it</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>For every cloud order, count its order_item rows alongside its total_paise</t>
+          <t>Would be: select from local_outbox / sync_replay_block on the edge SQLite file</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>No order with money on it and nothing in it</t>
+          <t>A count of pending and permanently-blocked rows</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>3 order(s) carry a non-zero total with ZERO lines. Per order: 01a090c4-a61b-7f12-96c3-3c549645821a status=DRAFT total_paise=30000 lines=0 | 01a090c4-f089-7693-8c1c-67e449530a77 status=SENT_TO_KITCHEN total_paise=4000 lines=2 | 01a090c9-4620-7f10-b560-de6bf75ec282 status=DRAFT total_paise=36000 lines=0 | 01a090c9-b837-7782-991c-21c7ecb4442b status=DRAFT total_paise=42000 lines=0</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>NOT TESTABLE from outside the POS process. The edge SQLite file is encrypted at rest and there is no read surface for the outbox — no Tauri command, no captain route and no LAN frame exposes it</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>NOT TESTABLE</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>SQL: 01a090c4-a61b-7f12-96c3-3c549645821a status=DRAFT total_paise=30000 lines=0 ; 01a090c4-f089-7693-8c1c-67e449530a77 status=SENT_TO_KITCHEN total_paise=4000 lines=2 ; 01a090c9-4620-7f10-b560-de6bf75ec282 status=DRAFT total_paise=36000 lines=0 ; 01a090c9-b837-7782-991c-21c7ecb4442b status=DRAFT total_paise=42000 lines=0</t>
+          <t>ADR-011: 'the edge SQLite file is encrypted at rest — never copy it or its backups anywhere unencrypted'</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>THE BACK OFFICE SHOWS AN ORDER FOR ₹300 WITH NOTHING IN IT. docs/backlog.md records every ItemAdded being refused on the variant foreign key, and this is that refusal seen from the cloud side: the order row and its item rows are separate outbox entries, so the parent lands and the children are rejected, leaving a total with no lines to explain it. S-SYNC-08 names the cause — 12 cloud menu items carry no variant at all. Demo step 6 reads from exactly this data.</t>
+          <t>This is gap A3's surfacing half seen from the outside: a stranded row is visible only on the POS window, which cannot be driven here. The cloud-side consequence is measurable and IS measured in S-SYNC-04.</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr"/>
@@ -4361,17 +4382,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-11</t>
+          <t>S-SYNC-07</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1a / 2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>The cloud actually holds the config it is the authority for</t>
+          <t>The cloud menu is seeded, so an admin price edit has something to edit</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4381,80 +4402,76 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>restaurant_table, station, printer, tax_profile and the menu are CONFIG, cloud-authoritative, syncing down (ADR-011, ADR-014). The edge caches them; the cloud owns them.</t>
+          <t>M6 C7 closed the cloud/edge seed drift as no longer needed</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Count each cloud-authoritative config table in Postgres</t>
+          <t>select count(*) from menu_item</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Non-zero for every table the outlet is currently using</t>
+          <t>Non-zero and comparable to the edge's 43</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>restaurant_table=0, station=0, printer=0, tax_profile=3, menu_category=10, menu_item=43, supplier=1. Empty cloud-side: restaurant_table, station, printer</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>43 menu_item rows in the cloud</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>SQL counts — restaurant_table=0, station=0, printer=0, tax_profile=3, menu_category=10, menu_item=43, supplier=1</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>THE TILL HAS TABLES AND STATIONS; THE CLOUD HAS NEITHER. They came from the edge dev seed, and config apply UPSERTS WITHOUT PRUNING (contracts 0.7.0), so a pull can never add them and can never remove them either — the outlet runs on config the cloud cannot reproduce, manage or show. For a demo whose pitch is 'manage it from the back office', every table on the waiter's phone and every station a KOT routes to is invisible to the back office. Note the asymmetry with menu_item, which IS seeded cloud-side and therefore IS editable in the admin console.</t>
-        </is>
-      </c>
+          <t>SQL count(menu_item) = 43</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>S-SYNC-12</t>
+          <t>S-SYNC-08</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1a / 6</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>A live POS keeps pumping for as long as it keeps serving</t>
+          <t>Cloud variant coverage matches the edge, so a replayed order item does not violate its FK</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>POS process -&gt; backend 8080 -&gt; postgres 5432</t>
+          <t>postgres 5432</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Two POS instances were observed this run. pid 74104 (started 14:04:44 UTC) and, after the operator restarted it, pid 80612 (started 14:31:36 UTC). The pump interval is 60s and S-SYNC-09 confirms pid 80612 hits it: contacts at 14:36:38, 14:37:39, 14:38:39.</t>
+          <t>M6 C3 found order_item_variant_id_fkey, not the menu_item seed, was the real refusal key</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Sample device_credential.last_used_at for the POS device across both instances and compare the contact pattern while each process was demonstrably still serving LAN requests</t>
+          <t>Histogram of variants per menu_item in the cloud</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Contact every ~60s for as long as the process is alive</t>
+          <t>Every item carrying at least the variants the edge offers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>pid 80612: contacts 60-61s apart, exactly as documented. pid 74104: LAST contact at 14:07:47, about three minutes after start, then NOTHING for the remaining ~12 minutes of its life — while it was still serving 9320 (S-CUI-01 recorded HTTP 200 and a real captain 401 body from it at 14:22) and still hosting 9310. It then exited without the operator touching it.</t>
+          <t>variants-per-item histogram (variants|items): 0|12, 1|9, 2|22</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
@@ -4464,12 +4481,12 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>docs/demo-screens/scenarios/pos-uplink-watch-instance-74104-stalled.txt (12 samples, one contact change in 19 minutes) against pos-uplink-watch-instance-80612-healthy.txt (14 samples, 60s cadence)</t>
+          <t>SQL histogram: 0|12 ; 1|9 ; 2|22</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>THE PUMP IS NOT SLOW — IT STOPPED, AND THE PROCESS DID NOT. This is worse than a long interval, because every outward sign of health stayed green: the till served the LAN, the captain listener answered, the KDS socket accepted clients. Nothing surfaced that the outlet had gone silent toward the cloud. MEASURED CONSEQUENCE: the WAITER device enrolled at 14:14:23 could not pair until 14:31:37 — seventeen minutes — because the config pull that delivers a credential to device_credential_cache rides this same loop, and what finally delivered it was the STARTUP pull of the replacement process, not a tick. NOT DIAGNOSED HERE: whether the pump thread died, wedged on the database lock, or the process was already failing. This run observed the symptom on one instance and could not reproduce it on the second, so it is reported as an observation with its artefacts, not as a root cause. The first measurement's own conclusion ('the pump interval is 12m27s') was WRONG and is superseded by this row: it spanned a process boundary, where a startup drain and a shutdown drain cannot be told apart from periodic ticks.</t>
+          <t>docs/backlog.md records every ItemAdded being refused on the variant foreign key. Items with zero cloud variants are the rows that cannot accept a replayed line.</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr"/>
@@ -4477,42 +4494,42 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>S-CHAIN-01</t>
+          <t>S-SYNC-09</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1a / 3</t>
+          <t>1a / 6</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>The KDS LAN socket accepts an authenticated client and delivers a ticket snapshot</t>
+          <t>The periodic sync pump contacts the cloud at its documented interval</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>POS process, ws 9310</t>
+          <t>POS process -&gt; backend 8080 -&gt; postgres 5432</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>POS process hosting the LAN hub; enrolled KDS device token from apps/kds/.env.dev</t>
+          <t>A5 landed a timer calling AppState::drain_outbox; DEFAULT_PERIODIC_DRAIN_INTERVAL is 60s (apps/pos/src-tauri/src/state.rs:93) and apps/pos/.env.dev sets no HOLLER_PERIODIC_DRAIN_INTERVAL_SECS override. The config pull runs FIRST on every tick, inside the same lock as the pump (ADR-024).</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Connect to /kds?outlet_id=..&amp;device_id=.., send the {type:auth} first frame, wait 2s</t>
+          <t>Sample device_credential.last_used_at for the POS device every 30s across a 7-minute window and measure the interval between distinct cloud contacts</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Socket opens, auth accepted, a snapshot frame arrives</t>
+          <t>Contact at least every 60s, so a newly enrolled device is usable within a minute</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Socket open; auth accepted (not closed); frames=2; snapshot carried 0 ticket(s)</t>
+          <t>Over 7 minutes of sampling the POS made 7 distinct cloud contact(s): 2026-09-11 15:29:37.744369+00 then 2026-09-11 15:30:38.211759+00 then 2026-09-11 15:31:39.180876+00 then 2026-09-11 15:32:39.606733+00 then 2026-09-11 15:33:39.968017+00 then 2026-09-11 15:34:40.499526+00 then 2026-09-11 15:35:40.862704+00. Longest observed gap between contacts: 1m1s against a documented 60s.</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -4522,84 +4539,386 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>live ws 9310 session held open by this stage</t>
+          <t>docs/demo-screens/scenarios/pos-uplink-watch.txt — 14 samples, window 2026-09-11 15:30:03.426109+00 to 2026-09-11 15:36:35.346498+00</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>A plain ws://host:9310 connect with no path and no auth frame is REJECTED at the handshake, which from outside is indistinguishable from the socket being down. The path and the first-frame auth are both required (apps/kds/src/lib/lanClient.ts:56-61).</t>
+          <t>MEASURED ON A PROCESS WATCHED STAYING UP THROUGHOUT, which is what makes the number mean anything: across a process start and a process stop, the startup drain and the shutdown drain are indistinguishable from periodic ticks, and a first attempt at this measurement spanned exactly that and had to be thrown away. See S-SYNC-12 for what that first attempt DID find, which is a different defect and a real one.</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>NEW ROW this re-run. The earlier pass never held a socket open across a send, so it could not separate 'the order was created' from 'the kitchen received it'.</t>
+          <t>WAS FAIL — 2 contacts in 6 minutes, longest gap 12m27s against a documented 60s, with the shutdown-drain alternative explicitly NOT excluded. NOW PASS: 7 contacts in 7 minutes, every gap 1m0s, measured on Postgres's clock. VERDICT ON STARTUP-PULL VERSUS PERIODIC-PULL: THE A5 PERIODIC PUMP IS NOT DEFECTIVE. It ticks at its documented interval on a healthy process. The earlier 12m27s gap belonged to the PREVIOUS process, which stopped pumping and then died minutes later — an instance that was already failing, not a design fault. So the pairing delay was a property of that sick process, not of the pump. NOTE WHAT THIS RUN DOES NOT SHOW: stage 01 REUSED the existing enrolment rather than minting a new credential, so no credential arrived from 401 to 200 during this run and the periodic pull was never watched delivering one. That it does is inferred from the proven 60s tick plus edge/sync/src/config.rs:770, not observed.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>S-SYNC-10</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>A replayed order carries its line items, not just its total</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>postgres 5432</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Orders have replayed (S-SYNC-01) and the cloud holds menu_item_variant rows</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>For every cloud order, count its order_item rows alongside its total_paise</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>No order with money on it and nothing in it</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>21 order(s) carry a non-zero total with ZERO lines. Per order: 01a090c4-a61b-7f12-96c3-3c549645821a status=DRAFT total_paise=30000 lines=0 | 01a090c4-f089-7693-8c1c-67e449530a77 status=SENT_TO_KITCHEN total_paise=4000 lines=2 | 01a090c9-4620-7f10-b560-de6bf75ec282 status=DRAFT total_paise=36000 lines=0 | 01a090c9-b837-7782-991c-21c7ecb4442b status=DRAFT total_paise=42000 lines=0 | 01a09111-4af5-75d0-a871-1db5129345f8 status=DRAFT total_paise=38000 lines=0 | 01a09111-d12a-7a43-8e74-2217e2d5abe3 status=DRAFT total_paise=38000 lines=0 | 01a09111-e468-7431-aacd-6b8f1ec5c12c status=DRAFT total_paise=38000 lines=0 | 01a09111-e84a-7482-ad93-236be923574b status=DRAFT total_paise=38000 lines=0 | 01a09112-3895-7572-a5ba-64d7f34eec98 status=DRAFT total_paise=38000 lines=0 | 01a09112-4bb3-7941-be34-762ea1baf2bb status=DRAFT total_paise=38000 lines=0 | 01a09112-4f72-72f2-af23-b081bfddac13 status=DRAFT total_paise=38000 lines=0 | 01a09112-84b2-7443-9be3-073a42173fc3 status=DRAFT total_paise=100 lines=0 | 01a09112-8866-7423-b797-7413889a4103 status=DRAFT total_paise=100 lines=0 | 01a09112-937c-7a03-801b-571253176bc2 status=DRAFT total_paise=100 lines=0 | 01a09112-9748-72e2-9399-824b95ffd971 status=DRAFT total_paise=2000 lines=0 | 01a09113-10f1-7140-bd7b-2da3fd153b52 status=DRAFT total_paise=100 lines=0 | 01a09113-14ca-73e0-9855-2b8fe183437e status=DRAFT total_paise=100 lines=0 | 01a09113-201b-7173-9cc0-56ab224651be status=DRAFT total_paise=100 lines=0 | 01a09113-23e3-73c1-9202-83e006cf26fa status=DRAFT total_paise=2000 lines=3 | 01a09113-f4e4-7de2-9905-603df58a95da status=DRAFT total_paise=100 lines=0 | 01a09113-f8af-7882-b5d9-32df1556f166 status=DRAFT total_paise=100 lines=0 | 01a09114-04b3-7ee3-9674-8d8125d41c76 status=DRAFT total_paise=100 lines=0 | 01a09114-08bd-7a73-9af1-ddd39e018190 status=DRAFT total_paise=2000 lines=3 | 01a09117-c3e3-73f3-be4b-93c5e5b74ce7 status=DRAFT total_paise=5500 lines=0</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>SQL: 01a090c4-a61b-7f12-96c3-3c549645821a status=DRAFT total_paise=30000 lines=0 ; 01a090c4-f089-7693-8c1c-67e449530a77 status=SENT_TO_KITCHEN total_paise=4000 lines=2 ; 01a090c9-4620-7f10-b560-de6bf75ec282 status=DRAFT total_paise=36000 lines=0 ; 01a090c9-b837-7782-991c-21c7ecb4442b status=DRAFT total_paise=42000 lines=0 ; 01a09111-4af5-75d0-a871-1db5129345f8 status=DRAFT total_paise=38000 lines=0 ; 01a09111-d12a-7a43-8e74-2217e2d5abe3 status=DRAFT total_paise=38000 lines=0 ; 01a09111-e468-7431-aacd-6b8f1ec5c12c status=DRAFT total_paise=38000 lines=0 ; 01a09111-e84a-7482-ad93-236be923574b status=DRAFT total_paise=38000 lines=0 ; 01a09112-3895-7572-a5ba-64d7f34eec98 status=DRAFT total_paise=38000 lines=0 ; 01a09112-4bb3-7941-be34-762ea1baf2bb status=DRAFT total_paise=38000 lines=0 ; 01a09112-4f72-72f2-af23-b081bfddac13 status=DRAFT total_paise=38000 lines=0 ; 01a09112-84b2-7443-9be3-073a42173fc3 status=DRAFT total_paise=100 lines=0 ; 01a09112-8866-7423-b797-7413889a4103 status=DRAFT total_paise=100 lines=0 ; 01a09112-937c-7a03-801b-571253176bc2 status=DRAFT total_paise=100 lines=0 ; 01a09112-9748-72e2-9399-824b95ffd971 status=DRAFT total_paise=2000 lines=0 ; 01a09113-10f1-7140-bd7b-2da3fd153b52 status=DRAFT total_paise=100 lines=0 ; 01a09113-14ca-73e0-9855-2b8fe183437e status=DRAFT total_paise=100 lines=0 ; 01a09113-201b-7173-9cc0-56ab224651be status=DRAFT total_paise=100 lines=0 ; 01a09113-23e3-73c1-9202-83e006cf26fa status=DRAFT total_paise=2000 lines=3 ; 01a09113-f4e4-7de2-9905-603df58a95da status=DRAFT total_paise=100 lines=0 ; 01a09113-f8af-7882-b5d9-32df1556f166 status=DRAFT total_paise=100 lines=0 ; 01a09114-04b3-7ee3-9674-8d8125d41c76 status=DRAFT total_paise=100 lines=0 ; 01a09114-08bd-7a73-9af1-ddd39e018190 status=DRAFT total_paise=2000 lines=3 ; 01a09117-c3e3-73f3-be4b-93c5e5b74ce7 status=DRAFT total_paise=5500 lines=0</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>THE BACK OFFICE SHOWS AN ORDER FOR ₹300 WITH NOTHING IN IT. docs/backlog.md records every ItemAdded being refused on the variant foreign key, and this is that refusal seen from the cloud side: the order row and its item rows are separate outbox entries, so the parent lands and the children are rejected, leaving a total with no lines to explain it. S-SYNC-08 names the cause — 12 cloud menu items carry no variant at all. Demo step 6 reads from exactly this data.</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>S-SYNC-11</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1a / 2</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>The cloud actually holds the config it is the authority for</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>postgres 5432</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>restaurant_table, station, printer, tax_profile and the menu are CONFIG, cloud-authoritative, syncing down (ADR-011, ADR-014). The edge caches them; the cloud owns them.</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Count each cloud-authoritative config table in Postgres</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Non-zero for every table the outlet is currently using</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>restaurant_table=0, station=0, printer=0, tax_profile=3, menu_category=10, menu_item=43, supplier=1. Empty cloud-side: restaurant_table, station, printer</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>SQL counts — restaurant_table=0, station=0, printer=0, tax_profile=3, menu_category=10, menu_item=43, supplier=1</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>THE TILL HAS TABLES AND STATIONS; THE CLOUD HAS NEITHER. They came from the edge dev seed, and config apply UPSERTS WITHOUT PRUNING (contracts 0.7.0), so a pull can never add them and can never remove them either — the outlet runs on config the cloud cannot reproduce, manage or show. For a demo whose pitch is 'manage it from the back office', every table on the waiter's phone and every station a KOT routes to is invisible to the back office. Note the asymmetry with menu_item, which IS seeded cloud-side and therefore IS editable in the admin console.</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>S-SYNC-12</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1a / 6</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>A live POS keeps pumping for as long as it keeps serving</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>POS process -&gt; backend 8080 -&gt; postgres 5432</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>holler-pos pid 55508 up for the whole sampling window (S-ENV-02), serving 9310 and 9320 throughout. The documented interval is 60s (DEFAULT_PERIODIC_DRAIN_INTERVAL, apps/pos/src-tauri/src/state.rs:93).</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Parse the committed uplink artefact — device_credential.last_used_at for the POS device sampled every 30s from outside the POS, on Postgres's clock — and measure the interval between distinct cloud contacts.</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Contact every ~60s for as long as the process is alive, with no gap beyond 2x the documented interval</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>7 distinct contact(s) over 2026-09-11 15:30:03.426109+00 to 2026-09-11 15:36:35.346498+00 (14 samples). Longest gap between contacts: 1m1s against a documented 60s.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>docs/demo-screens/scenarios/pos-uplink-watch.txt — 2026-09-11 15:30:03.426109+00 to 2026-09-11 15:36:35.346498+00 (14 samples)</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>HISTORICAL FINDING, FROM AN EARLIER RUN, RETAINED BECAUSE IT WAS REAL AND IS NOT DISPROVED BY A HEALTHY WINDOW: on pid 74104, THE PUMP IS NOT SLOW — IT STOPPED, AND THE PROCESS DID NOT. This is worse than a long interval, because every outward sign of health stayed green: the till served the LAN, the captain listener answered, the KDS socket accepted clients. Nothing surfaced that the outlet had gone silent toward the cloud. MEASURED CONSEQUENCE: the WAITER device enrolled at 14:14:23 could not pair until 14:31:37 — seventeen minutes — because the config pull that delivers a credential to device_credential_cache rides this same loop, and what finally delivered it was the STARTUP pull of the replacement process, not a tick. NOT DIAGNOSED HERE: whether the pump thread died, wedged on the database lock, or the process was already failing. This run observed the symptom on one instance and could not reproduce it on the second, so it is reported as an observation with its artefacts, not as a root cause. The first measurement's own conclusion ('the pump interval is 12m27s') was WRONG and is superseded by this row: it spanned a process boundary, where a startup drain and a shutdown drain cannot be told apart from periodic ticks.</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>WAS FAIL, carried as literal text from an earlier run against pids 74104 and 80612, both long gone — a row that could never change verdict no matter what the live process did. NOW RE-MEASURED against pid 55508 from the committed artefact. THE HISTORICAL FINDING IS NOT WITHDRAWN: a healthy window does not prove the stall cannot recur, only that this process did not stall during this window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>S-SYNC-13</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1a / 6</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>The till's own devseed device has no cloud `device` row, so till-authored orders replay unattributable</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>postgres 5432</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Orders authored by the till before this run, replayed into the cloud</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Left join "order".device_id to device.id and list every order that fails to resolve</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Zero orders with an unresolvable device_id</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>4 order(s) do not resolve: 01a090c4-a61b-7f12-96c3-3c549645821a device_id=0191a000-0000-7000-8000-00000000000b at 2026-09-11 14:00:01.819+00 | 01a090c4-f089-7693-8c1c-67e449530a77 device_id=0191a000-0000-7000-8000-00000000000b at 2026-09-11 14:00:20.873+00 | 01a090c9-4620-7f10-b560-de6bf75ec282 device_id=0191a000-0000-7000-8000-00000000000b at 2026-09-11 14:05:04.928+00 | 01a090c9-b837-7782-991c-21c7ecb4442b device_id=0191a000-0000-7000-8000-00000000000b at 2026-09-11 14:05:34.135+00</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>SQL: select o.id from "order" o left join device d on d.id=o.device_id where d.id is null -&gt; 4 row(s)</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>NOT THE T30 DEFECT AND NOT FIXED BY IT. devseed mints the till's `device` row directly in edge SQLite (edge/database/src/bin/devseed.rs:41) and nothing ever enrols it with the backend, so the cloud has no row to join to. Back-office attribution for till-authored orders is therefore blank — which is the same class of defect T30 fixed, pointed the other way down the wire. Recorded, not fixed: enrolling the till is a change to the seed path, outside this task's read-only scope.</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>NEW ROW this run. Split out of S-SYNC-03, which previously reported both gaps as one verdict and so could not show that the captain path had been fixed while the till path had not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>S-CHAIN-01</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1a / 3</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>The KDS LAN socket accepts an authenticated client and delivers a ticket snapshot</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>POS process, ws 9310</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>POS process hosting the LAN hub; enrolled KDS device token from apps/kds/.env.dev</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Connect to /kds?outlet_id=..&amp;device_id=.., send the {type:auth} first frame, wait 2s</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Socket opens, auth accepted, a snapshot frame arrives</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Socket open; auth accepted (not closed); frames=1; snapshot carried 0 ticket(s)</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>live ws 9310 session held open by this stage</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>A plain ws://host:9310 connect with no path and no auth frame is REJECTED at the handshake, which from outside is indistinguishable from the socket being down. The path and the first-frame auth are both required (apps/kds/src/lib/lanClient.ts:56-61).</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>NEW ROW this re-run. The earlier pass never held a socket open across a send, so it could not separate 'the order was created' from 'the kitchen received it'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>S-CHAIN-02</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>THE CENTRAL CLAIM — pair, pick a table, add an item with a free modifier, send, and the KOT arrives on the KDS socket</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>captain 9320 -&gt; edge db -&gt; ws 9310</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Paired WAITER device; table T1; item "Butter Chicken" with free modifier "Spice/Hot"; socket held open from S-CHAIN-01 BEFORE the send</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>POST /api/orders (1 line, default variant, one 0-paise modifier) -&gt; POST /api/orders/{id}/send -&gt; count frames that arrived on the socket opened beforehand</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>201 created, 200 sent, at least one KOT frame on the socket</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>CHAIN STOPS AT CREATE. POST /api/orders -&gt; HTTP 400 {"code":"STORAGE_ERROR","message":"sqlite error: FOREIGN KEY constraint failed"}. Nothing was sent, so no KOT frame could arrive and the socket stayed silent.</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>live captain listener + live ws 9310, same process</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>The free modifier is deliberate: a 0-paise modifier still has to reach the stored line, and a price-changing one would hide a dropped modifier behind a changed total.</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>RE-RUN with the POS back up. The chain now gets further than before — pairing, tables and menu all succeed — but it stops at order create, which the earlier run could not reach at all.</t>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Created 01a09112-3895-7572-a5ba-64d7f34eec98 (display #A9); send 200 cutting 1 KOT(s); 1 frame(s) arrived on the pre-opened socket after the send, 1 of them naming THIS order. Frame types: kot_upserted.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>live captain listener + live ws 9310, same process (holler-pos pid 55508)</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>The free modifier is deliberate: a 0-paise modifier still has to reach the stored line, and a price-changing one would hide a dropped modifier behind a changed total. The socket was opened in S-CHAIN-01 BEFORE the create and held across the send, so 'the order was created' and 'the kitchen received it' are asserted separately — and the frame is matched against THIS order's id, so an unrelated ticket or a heartbeat cannot satisfy it.</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>WAS FAIL (create refused, 400 FOREIGN KEY constraint failed). NOW PASS end to end on the fixed binary. Two things changed: 758a70b mints the device row the order's device_id references, and this stage was reading the create response's `id` instead of `holler_order_id`, so the first post-fix run sent to /api/orders/undefined/send and reported a 201 create as 'the chain stops at create'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L70"/>
+  <autoFilter ref="A1:L75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4610,7 +4929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4620,7 +4939,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Holler demo scenario run</t>
         </is>
@@ -4643,445 +4962,342 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RE-RUN 2026-09-11 against holler-pos pid 80612 (started 20:01:36 IST). The Re-run column says why each moved row moved; an empty Re-run cell means the row was recorded once and never revisited, not that it was re-confirmed.</t>
+          <t>RE-RUN T30, 2026-09-11, against holler-pos pid 55508 (started 20:50:29 IST, binary built 20:50:27 — after fix 758a70b). The Re-run column says why each moved row moved; an empty Re-run cell means the row was recorded once and never revisited, not that it was re-confirmed.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WHAT T30 CHANGED: config apply now mints the `device` row a credential references, so a waiter's phone can be the device_id on an order. The step-1a chain completes end to end — order created, KOT delivered on a socket held open across the send, rendered on the KDS, bumped, and the bump survived a reload. CARRY THE SCOPE LIMIT WITH THE RESULT: the fix only fires for credentials that ARRIVE in a config bundle, and a credential already cached is never re-sent, so every device paired BEFORE the fix stays broken (S-CAP-20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Counts by status</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>NOT TESTABLE</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="B12" s="13" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Top failures, most severe first</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Demo step</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>What actually happened</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>S-CHAIN-02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>S-CAP-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>THE CENTRAL CLAIM — pair, pick a table, add an item with a free modifier, send, and the KOT arrives on the KDS socket</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>CHAIN STOPS AT CREATE. POST /api/orders -&gt; HTTP 400 {"code":"STORAGE_ERROR","message":"sqlite error: FOREIGN KEY constraint failed"}. Nothing was sent, so no KOT frame could arrive and the socket stayed silent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>S-CAP-19</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>A device paired BEFORE the fix stays permanently broken — the fix has no backfill</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Pre-fix device -&gt; HTTP 400 still "FOREIGN KEY constraint failed", while the post-fix device created successfully seconds earlier on the same process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>S-SYNC-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>A replayed order carries its line items, not just its total</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>21 order(s) carry a non-zero total with ZERO lines. Per order: 01a090c4-a61b-7f12-96c3-3c549645821a status=DRAFT total_paise=30000 lines=0 | 01a090c4-f089-7693-8c1c-67e449530a77 status=SENT_TO_KITCHEN total_paise=4000 lines=2 | 01a090c9-4620-7f10-b560-de6bf75ec282 status=DRAFT total_paise=36000 lines=0 | 01a090c9-b837-7782-991c-21c7ecb4442b status=DRAFT total_paise=42000 lines=0 | 01a09111-4af5-75d0-a871-1db5129345f8 status=DRAFT total_paise=38000 lines=0 | 01a09111-d12a-7a43-8e74-2217e2d5abe3 status=DRAFT total_paise=38000 lines=0 | 01a09111-e468-7431-aacd-6b8f1ec5c12c status=DRAFT total_paise=38000 lines=0 | 01a09111-e84a-7482-ad93-236be923574b status=DRAFT total_paise=38000 lines=0 | 01a09112-3895-7572-a5ba-64d7f34eec98 status=DRAFT total_paise=38000 lines=0 | 01a09112-4bb3-7941-be34-762ea1baf2bb status=DRAFT total_paise=38000 lines=0 | 01a09112-4f72-72f2-af23-b081bfddac13 status=DRAFT total_paise=38000 lines=0 | 01a09112-84b2-7443-9be3-073a42173fc3 status=DRAFT total_paise=100 lines=0 | 01a09112-8866-7423-b797-7413889a4103 status=DRAFT total_paise=100 lines=0 | 01a09112-937c-7a03-801b-571253176bc2 status=DRAFT total_paise=100 lines=0 | 01a09112-9748-72e2-9399-824b95ffd971 status=DRAFT total_paise=2000 lines=0 | 01a09113-10f1-7140-bd7b-2da3fd153b52 status=DRAFT total_paise=100 lines=0 | 01a09113-14ca-73e0-9855-2b8fe183437e status=DRAFT total_paise=100 lines=0 | 01a09113-201b-7173-9cc0-56ab224651be status=DRAFT total_paise=100 lines=0 | 01a09113-23e3-73c1-9202-83e006cf26fa status=DRAFT total_paise=2000 lines=3 | 01a09113-f4e4-7de2-9905-603df58a95da status=DRAFT total_paise=100 lines=0 | 01a09113-f8af-7882-b5d9-32df1556f166 status=DRAFT total_paise=100 lines=0 | 01a09114-04b3-7ee3-9674-8d8125d41c76 status=DRAFT total_paise=100 lines=0 | 01a09114-08bd-7a73-9af1-ddd39e018190 status=DRAFT total_paise=2000 lines=3 | 01a09117-c3e3-73f3-be4b-93c5e5b74ce7 status=DRAFT total_paise=5500 lines=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>S-SYNC-08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Isolate the column whose foreign key stops every captain order create</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Both probes -&gt; 400 STORAGE_ERROR "sqlite error: FOREIGN KEY constraint failed". Removing the table, the modifier and the variant delta changes nothing, so the failing key is NOT table_id, menu_item_id, variant_id or modifier_id — all of those were varied or removed. The only foreign key left on the insert is order.device_id, which is "TEXT NOT NULL REFERENCES device(id)" (packages/contracts/sqlite/0035_order_source_widened.sql:53).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>S-CAP-10</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Cloud variant coverage matches the edge, so a replayed order item does not violate its FK</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>variants-per-item histogram (variants|items): 0|12, 1|9, 2|22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>S-SYNC-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1a / 2</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>The cloud actually holds the config it is the authority for</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>restaurant_table=0, station=0, printer=0, tax_profile=3, menu_category=10, menu_item=43, supplier=1. Empty cloud-side: restaurant_table, station, printer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>S-SYNC-04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4 / 5 / 6</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>KNOWN GAP A7 — aggregates other than `order` never reach the cloud</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>kot=0, invoice=0, payment=0, stock_count=0, stock_ledger_entry=39, cash_shift=0, table_session=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>S-SYNC-13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1a / 6</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>The till's own devseed device has no cloud `device` row, so till-authored orders replay unattributable</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>4 order(s) do not resolve: 01a090c4-a61b-7f12-96c3-3c549645821a device_id=0191a000-0000-7000-8000-00000000000b at 2026-09-11 14:00:01.819+00 | 01a090c4-f089-7693-8c1c-67e449530a77 device_id=0191a000-0000-7000-8000-00000000000b at 2026-09-11 14:00:20.873+00 | 01a090c9-4620-7f10-b560-de6bf75ec282 device_id=0191a000-0000-7000-8000-00000000000b at 2026-09-11 14:05:04.928+00 | 01a090c9-b837-7782-991c-21c7ecb4442b device_id=0191a000-0000-7000-8000-00000000000b at 2026-09-11 14:05:34.135+00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>S-ADM-08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Orders screen</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>NOT BUILT. The admin console has three tabs — Menu and pricing, Suppliers, Goods receipts. There is no orders screen, no order route in apps/admin/src/lib/api.ts, and no component for one. Demo step 4 has no surface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>S-ADM-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Stock variance screen</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>NOT BUILT. No stock, variance or count screen exists in the admin console and no inventory endpoint is wired into apps/admin/src/lib/api.ts. Demo step 5 has no surface — and gap A7 means the underlying stock_count rows never reach the cloud either (S-SYNC-04), so the data is absent as well as the screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>S-CAP-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>A waiter creates an order on a table from the captain API</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 400; order_id=n/a; status=n/a; lines=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>S-CAP-18</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1a</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Isolate WHICH foreign key the captain order create violates</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>real table + real item + real variant: HTTP 400 STORAGE_ERROR | bogus table_id: HTTP 400 STORAGE_ERROR | bogus menu_item_id: HTTP 400 STORAGE_ERROR | bogus variant_id: HTTP 400 STORAGE_ERROR | TAKEAWAY, table_id null: HTTP 400 STORAGE_ERROR. All five identical = true</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>S-CUI-08</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1a</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Sending from the phone reaches the 'Sent to the kitchen' screen with the KOT list</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Still on the cart. Error: "sqlite error: FOREIGN KEY constraint failed"</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>S-SYNC-10</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>A replayed order carries its line items, not just its total</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>3 order(s) carry a non-zero total with ZERO lines. Per order: 01a090c4-a61b-7f12-96c3-3c549645821a status=DRAFT total_paise=30000 lines=0 | 01a090c4-f089-7693-8c1c-67e449530a77 status=SENT_TO_KITCHEN total_paise=4000 lines=2 | 01a090c9-4620-7f10-b560-de6bf75ec282 status=DRAFT total_paise=36000 lines=0 | 01a090c9-b837-7782-991c-21c7ecb4442b status=DRAFT total_paise=42000 lines=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>S-SYNC-11</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1a / 2</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>The cloud actually holds the config it is the authority for</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>restaurant_table=0, station=0, printer=0, tax_profile=3, menu_category=10, menu_item=43, supplier=1. Empty cloud-side: restaurant_table, station, printer</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>S-SYNC-12</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1a / 6</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>A live POS keeps pumping for as long as it keeps serving</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>pid 80612: contacts 60-61s apart, exactly as documented. pid 74104: LAST contact at 14:07:47, about three minutes after start, then NOTHING for the remaining ~12 minutes of its life — while it was still serving 9320 (S-CUI-01 recorded HTTP 200 and a real captain 401 body from it at 14:22) and still hosting 9310. It then exited without the operator touching it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>S-SYNC-04</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>4 / 5 / 6</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>KNOWN GAP A7 — aggregates other than `order` never reach the cloud</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>kot=0, invoice=0, payment=0, stock_count=0, stock_ledger_entry=39, cash_shift=0, table_session=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>S-ADM-08</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Orders screen</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>NOT BUILT. The admin console has three tabs — Menu and pricing, Suppliers, Goods receipts. There is no orders screen, no order route in apps/admin/src/lib/api.ts, and no component for one. Demo step 4 has no surface.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>S-ADM-09</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Stock variance screen</t>
+          <t>Every menu item carries at least one variant, so no line needs a null variant_id</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>NOT BUILT. No stock, variance or count screen exists in the admin console and no inventory endpoint is wired into apps/admin/src/lib/api.ts. Demo step 5 has no surface — and gap A7 means the underlying stock_count rows never reach the cloud either (S-SYNC-04), so the data is absent as well as the screen.</t>
+          <t>12 of 43 items have no variant: Aloo Tikki Chaat, Egg Bhurji, Filter Coffee, Gajar Halwa, Gulab Jamun (2 pc), …</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>S-SYNC-03</t>
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>S-API-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>A replayed order's device_id resolves to a real device row in the cloud</t>
+          <t>PATCH /menu/items/{itemId} refuses an identity field rather than ignoring it</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Across all orders: &lt;no device row&gt; x4</t>
+          <t>HTTP 400 invalid_input</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>S-SYNC-08</t>
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>S-BE-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>pre</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Cloud variant coverage matches the edge, so a replayed order item does not violate its FK</t>
+          <t>A rate-limited login is indistinguishable from a wrong password</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>variants-per-item histogram (variants|items): 0|12, 1|9, 2|22</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>S-BE-09</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>A rate-limited login is indistinguishable from a wrong password</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
           <t>HTTP 401 {"code":"unauthorized","message":"authentication required"} for a correct password, identical to the wrong-password body; no Retry-After; recovery only by waiting out the window</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>S-CAP-06</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1a</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Every menu item carries at least one variant, so no line needs a null variant_id</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>12 of 43 items have no variant: Aloo Tikki Chaat, Egg Bhurji, Filter Coffee, Gajar Halwa, Gulab Jamun (2 pc), …</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>S-API-02</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>PATCH /menu/items/{itemId} refuses an identity field rather than ignoring it</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 400 invalid_input</t>
         </is>
       </c>
     </row>
